--- a/Catálogo ROP-LOP 2027.xlsx
+++ b/Catálogo ROP-LOP 2027.xlsx
@@ -19,27 +19,54 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={13e6d1cf-ed57-4279-91bc-5c886f201b9b}</author>
-    <author>tc={3ce3c437-15dd-4a3f-8f1c-a331284ffb19}</author>
-    <author>tc={5248a60e-f01d-4dbc-8a99-ad017cf9f49b}</author>
-    <author>tc={a1233d24-e3c5-4049-a87c-5083df344ae2}</author>
-    <author>tc={b23add08-53d8-4b43-a715-84ae107323f1}</author>
-    <author>tc={c743d331-7ec0-4487-86f4-79a5044ac75e}</author>
-    <author>tc={c7789d2a-e7d4-4a94-80c3-6be96096b045}</author>
-    <author>tc={d21d91eb-35ca-41c8-94a6-ed7c92b21572}</author>
-    <author>tc={dd6ac2d0-9edd-46b4-b0ef-33f174cf3d44}</author>
+    <author>tc={084650f0-ece0-464c-b53c-a4306a96e34a}</author>
+    <author>tc={22233615-6a31-45f6-85e9-d87008445735}</author>
+    <author>tc={3cf0f526-fed6-4970-8110-6c1a561ba207}</author>
+    <author>tc={441d2b04-d373-4a9c-af6a-4de0d1fdb33e}</author>
+    <author>tc={4e3e344e-aaf2-4972-b3a3-c64713db101d}</author>
+    <author>tc={69da3166-d45c-4dff-ac98-f25200ba1c98}</author>
+    <author>tc={8100cc0a-5966-42ae-82f9-381e2e5b42a8}</author>
+    <author>tc={89ccc38b-d7c7-4962-bad4-c5abec74ef0e}</author>
+    <author>tc={a00864eb-706e-440e-8ebc-5902fb965ff6}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{13e6d1cf-ed57-4279-91bc-5c886f201b9b}" ref="I119">
+    <comment authorId="0" xr:uid="{084650f0-ece0-464c-b53c-a4306a96e34a}" ref="F16">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Tiene recurso propio
+	Actualmente cuenta con una clasificación programática con letra E
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{3ce3c437-15dd-4a3f-8f1c-a331284ffb19}" ref="H33">
+    <comment authorId="1" xr:uid="{22233615-6a31-45f6-85e9-d87008445735}" ref="F85">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Actalmente es un Lineamiento de Operación
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{3cf0f526-fed6-4970-8110-6c1a561ba207}" ref="F16">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Actualmente cuenta con clasificación Programpatica  E
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{441d2b04-d373-4a9c-af6a-4de0d1fdb33e}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	De momento se registra el nombre del componente; a la espera de nombre de la ROP.
+</t>
+      </text>
+    </comment>
+    <comment authorId="4" xr:uid="{4e3e344e-aaf2-4972-b3a3-c64713db101d}" ref="H33">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -48,16 +75,16 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{5248a60e-f01d-4dbc-8a99-ad017cf9f49b}" ref="A1">
+    <comment authorId="5" xr:uid="{69da3166-d45c-4dff-ac98-f25200ba1c98}" ref="I121">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	De momento se registra el nombre del componente; a la espera de nombre de la ROP.
+	Solo tiene recurso propio
 </t>
       </text>
     </comment>
-    <comment authorId="3" xr:uid="{a1233d24-e3c5-4049-a87c-5083df344ae2}" ref="I37">
+    <comment authorId="6" xr:uid="{8100cc0a-5966-42ae-82f9-381e2e5b42a8}" ref="I37">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -66,25 +93,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="4" xr:uid="{b23add08-53d8-4b43-a715-84ae107323f1}" ref="I121">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Solo tiene recurso propio
-</t>
-      </text>
-    </comment>
-    <comment authorId="5" xr:uid="{c743d331-7ec0-4487-86f4-79a5044ac75e}" ref="F16">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Actualmente cuenta con una clasificación programática con letra E
-</t>
-      </text>
-    </comment>
-    <comment authorId="6" xr:uid="{c7789d2a-e7d4-4a94-80c3-6be96096b045}" ref="A1">
+    <comment authorId="7" xr:uid="{89ccc38b-d7c7-4962-bad4-c5abec74ef0e}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -93,21 +102,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="7" xr:uid="{d21d91eb-35ca-41c8-94a6-ed7c92b21572}" ref="F85">
+    <comment authorId="8" xr:uid="{a00864eb-706e-440e-8ebc-5902fb965ff6}" ref="I119">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Actalmente es un Lineamiento de Operación
-</t>
-      </text>
-    </comment>
-    <comment authorId="8" xr:uid="{dd6ac2d0-9edd-46b4-b0ef-33f174cf3d44}" ref="F16">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Actualmente cuenta con clasificación Programpatica  E
+	Tiene recurso propio
 </t>
       </text>
     </comment>
@@ -196,1032 +196,1032 @@
     <t>Programa Becas Universitarias Al Estilo Jalisco</t>
   </si>
   <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>ROP</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
     <t>SG1_CH</t>
   </si>
   <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>LOP</t>
+  </si>
+  <si>
+    <t>Programa por la Inclusión de Personas con Discapacidad</t>
+  </si>
+  <si>
     <t>U</t>
   </si>
   <si>
+    <t>005</t>
+  </si>
+  <si>
     <t>SG1_C1</t>
   </si>
   <si>
-    <t>Programa por la Inclusión de Personas con Discapacidad</t>
+    <t>Apoyos a OSC para apoyo a la población de diversidad sexual</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>Atención y Oportunidades para las Juventudes No dejar a nadie atrás</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>Programa Red de enlaces regionales del Mecanismo de Atención a Víctimas de Discriminación MAViD MAViDmun</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>Comisión Estatal Indígena</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Apoyos económicos para los pueblos y comunidades indígenas</t>
   </si>
   <si>
     <t>SG1_C6</t>
   </si>
   <si>
-    <t>Apoyos a OSC para apoyo a la población de diversidad sexual</t>
+    <t>009</t>
+  </si>
+  <si>
+    <t>Becas por la Interculturalidad para estudiantes indígenas del nivel medio superior y superior</t>
+  </si>
+  <si>
+    <t>801</t>
+  </si>
+  <si>
+    <t>Comisión para la Búsqueda de Personas</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programa de Apoyo a Familiares de Personas Desaparecidas en el Estado de Jalisco </t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretaría de Hacienda </t>
+  </si>
+  <si>
+    <t>729</t>
+  </si>
+  <si>
+    <t>Fideicomiso de Administración para la mejora de la Seguridad Vial</t>
+  </si>
+  <si>
+    <t>011</t>
   </si>
   <si>
     <t>SG1_CA</t>
   </si>
   <si>
-    <t>Atención y Oportunidades para las Juventudes No dejar a nadie atrás</t>
+    <t>Renovación parque vehicular transporte público</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>Reducción de la tarifa del transporte público para las personas usuarias</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretaría de Educación </t>
+  </si>
+  <si>
+    <t>097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programa Ayuda Económica para NIñas del Internado Beatriz Hernández </t>
+  </si>
+  <si>
+    <t>098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becas Jalisco Contigo </t>
+  </si>
+  <si>
+    <t>099</t>
   </si>
   <si>
     <t>SG1_C5</t>
   </si>
   <si>
-    <t>Programa Red de enlaces regionales del Mecanismo de Atención a Víctimas de Discriminación MAViD MAViDmun</t>
-  </si>
-  <si>
-    <t>172</t>
+    <t xml:space="preserve">Becas Talento </t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programa Ayuda Económica para las y los Estudiantes de la Escuela Normal Rural Miguel Hidalgo </t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>Secretaría de Desarrollo Económico</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>Jalisco Atrae</t>
   </si>
   <si>
     <t>02_172</t>
   </si>
   <si>
-    <t>Comisión Estatal Indígena</t>
+    <t>014</t>
   </si>
   <si>
     <t>SJ7_C1</t>
   </si>
   <si>
-    <t xml:space="preserve"> Apoyos económicos para los pueblos y comunidades indígenas</t>
+    <t>Artesanías Jalisco Más</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>Impulso Mipymes Jalisco</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>Fondo Impulso Jalisco</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>Impulso a la Competitividad, Talento y Vinculación al estilo Jalisco</t>
   </si>
   <si>
     <t>SJ7_C2</t>
   </si>
   <si>
-    <t>Becas por la Interculturalidad para estudiantes indígenas del nivel medio superior y superior</t>
-  </si>
-  <si>
-    <t>801</t>
+    <t>017</t>
+  </si>
+  <si>
+    <t>Crecer al Estilo Jalisco mediante la generación de Empleo y Talento</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>Secretaría de Turismo</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>Programa para Desarrollo de productos y experiencias turísticas en el Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>Programa de apoyo a Producciones fílmicas y audiovisuales en el Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>Secretaría de Agricultura y Desarrollo Rural</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>Impulso Agro Jalisco. Producción y Tecnología</t>
   </si>
   <si>
     <t>02_801</t>
   </si>
   <si>
-    <t>Comisión para la Búsqueda de Personas</t>
-  </si>
-  <si>
     <t>SBP_GA</t>
   </si>
   <si>
-    <t xml:space="preserve">Programa de Apoyo a Familiares de Personas Desaparecidas en el Estado de Jalisco </t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>ROP</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Hacienda </t>
-  </si>
-  <si>
-    <t>729</t>
+    <t>021</t>
+  </si>
+  <si>
+    <t>Jalisco Agrosustentable</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>Eficiencia verde cañera</t>
   </si>
   <si>
     <t>03_729</t>
   </si>
   <si>
-    <t>LOP</t>
-  </si>
-  <si>
-    <t>Fideicomiso de Administración para la mejora de la Seguridad Vial</t>
+    <t>023</t>
   </si>
   <si>
     <t>ST4_D1</t>
   </si>
   <si>
-    <t>Renovación parque vehicular transporte público</t>
-  </si>
-  <si>
-    <t>005</t>
-  </si>
-  <si>
-    <t>006</t>
+    <t>Proyectos Estratégicos Agropecuarios, Pesqueros y Acuícolas al estilo Jalisco</t>
+  </si>
+  <si>
+    <t>024</t>
+  </si>
+  <si>
+    <t>Proyectos Estratégicos Agroalimentarios.</t>
+  </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>Empedrados al estilo Jalisco</t>
+  </si>
+  <si>
+    <t>026</t>
   </si>
   <si>
     <t>ST4_D2</t>
   </si>
   <si>
-    <t>Reducción de la tarifa del transporte público para las personas usuarias</t>
-  </si>
-  <si>
-    <t>007</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>Secretaría de Desarrollo Económico</t>
+    <t>Fondo Jalisco para Contingencias Agroalimentarias</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>Apoyo a Cooperativas de la Laguna de Cajititlán</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>Fortalecimiento de Casas Ejidales</t>
   </si>
   <si>
     <t>07_000</t>
   </si>
   <si>
+    <t>029</t>
+  </si>
+  <si>
     <t>S70_D1</t>
   </si>
   <si>
-    <t>Jalisco Atrae</t>
-  </si>
-  <si>
-    <t>008</t>
+    <t>Agroinnovadoras y Jóvenes del campo de Jalisco</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>Fideicomiso para Coberturas de Precios de Maíz</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>Fideicomiso para Coberturas de Precios de Maíz (LOP)</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>Agencia Estatal de Sanidad, Inocuidad y Calidad Agroalimentaria en Jalisco</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>Programa de Apoyo para el Fortalecimiento de la Inocuidad en Rastros en el Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>032</t>
   </si>
   <si>
     <t>S71_C1</t>
   </si>
   <si>
-    <t>Artesanías Jalisco Más</t>
-  </si>
-  <si>
-    <t>009</t>
+    <t>Programa de Eliminación de Animales Positivos, Reactores, Expuestos y Sospechosos</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>Programa de Apoyo para la Prevención y Control del Gusano Barrenador del Ganado en el Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretaría de Medio Ambiente y Desarrollo Territorial </t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O.P.D. Bosque la Primavera </t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>Administración y Manejo del Área de Protección de Flora y Fauna La Primavera</t>
+  </si>
+  <si>
+    <t>043</t>
   </si>
   <si>
     <t>S72_B1</t>
   </si>
   <si>
-    <t>Impulso Mipymes Jalisco</t>
-  </si>
-  <si>
-    <t>010</t>
-  </si>
-  <si>
-    <t>244</t>
+    <t>Fideicomiso para la Administración del Programa de Desarrollo Forestal del Estado de Jalisco (FIPRODEFO)</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>Programa para el Desarrollo Forestal Sustentable del Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Secretaría del Sistema de Asistencia Social</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yo Jalisco Apoyo para la Salud Mental </t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>Yo Jalisco, Apoyo al Transporte</t>
   </si>
   <si>
     <t>07_244</t>
   </si>
   <si>
-    <t>Fondo Impulso Jalisco</t>
-  </si>
-  <si>
-    <t>011</t>
+    <t>038</t>
   </si>
   <si>
     <t>S7F_C1</t>
   </si>
   <si>
-    <t>Impulso a la Competitividad, Talento y Vinculación al estilo Jalisco</t>
-  </si>
-  <si>
-    <t>012</t>
-  </si>
-  <si>
-    <t>04</t>
+    <t>Yo Jalisco Apoyo a Personas Cuidadoras y Personas Dependientes de Cuidados</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>Yo Jalisco Apoyo para el Cuidado Infantil</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>Yo Jalisco, Apoyo a Instituciones de Cuidado Infantil</t>
+  </si>
+  <si>
+    <t>041</t>
   </si>
   <si>
     <t>S7F_C2</t>
   </si>
   <si>
-    <t xml:space="preserve">Secretaría de Educación </t>
-  </si>
-  <si>
-    <t>Crecer al Estilo Jalisco mediante la generación de Empleo y Talento</t>
-  </si>
-  <si>
-    <t>097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programa Ayuda Económica para NIñas del Internado Beatriz Hernández </t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>Secretaría de Turismo</t>
+    <t xml:space="preserve">Yo Jalisco Apoyo a Jefas de Jalisco </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listo Jalisco </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yo Jalisco Apoyo a Asociaciones Civiles </t>
   </si>
   <si>
     <t>08_000</t>
   </si>
   <si>
+    <t>044</t>
+  </si>
+  <si>
     <t>S81_03</t>
   </si>
   <si>
-    <t>Programa para Desarrollo de productos y experiencias turísticas en el Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Becas Jalisco Contigo </t>
-  </si>
-  <si>
-    <t>099</t>
+    <t>Yo Jalisco, Apoyo a Nuestras Comunidades</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>Yo Jalisco, Apoyo al Desarrollo Social</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>Enchulemos Jalisco</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>Yo Jalisco Transporte a Grupos Prioritarios</t>
   </si>
   <si>
     <t>S81_06</t>
   </si>
   <si>
-    <t>Programa de apoyo a Producciones fílmicas y audiovisuales en el Estado de Jalisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Becas Talento </t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>Secretaría de Agricultura y Desarrollo Rural</t>
+    <t>048</t>
+  </si>
+  <si>
+    <t>Yo Jalisco, Apoyo para nuestra gente</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Secretaría de Innovación, Ciencia y Tecnológia</t>
+  </si>
+  <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>Fortalecimiento de ecosistemas regionales a través de la innovación y emprendimiento</t>
   </si>
   <si>
     <t>09_000</t>
   </si>
   <si>
-    <t xml:space="preserve">Programa Ayuda Económica para las y los Estudiantes de la Escuela Normal Rural Miguel Hidalgo </t>
+    <t>050</t>
   </si>
   <si>
     <t>S91_D8</t>
   </si>
   <si>
-    <t>Impulso Agro Jalisco. Producción y Tecnología</t>
-  </si>
-  <si>
-    <t>013</t>
+    <t>Fortalecimiento de la Cultura de Innovación, Ciencia y Tecnología</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>Apoyos de Educación Superior para Jóvenes LEGADO</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>Impulso y Fortalecimiento a la Educación Superior</t>
+  </si>
+  <si>
+    <t>067</t>
+  </si>
+  <si>
+    <t>Consejo Estatal de Ciencia y Tecnología del Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>053</t>
   </si>
   <si>
     <t>S92_D1</t>
   </si>
   <si>
-    <t>Jalisco Agrosustentable</t>
+    <t>Gestión de fondos y programas de apoyo a la Ciencia, Tecnología e Innovación</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Agencia para el Desarrollo de Industrias Creativas y Digitales del Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>Fondo para Proyectos de Alto Impacto a la Industria Creativa Digital</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>Fondo Jalisco Creativo</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura</t>
+  </si>
+  <si>
+    <t>Secretaría de cultura</t>
   </si>
   <si>
     <t>S92_D2</t>
   </si>
   <si>
-    <t>Eficiencia verde cañera</t>
-  </si>
-  <si>
-    <t>014</t>
+    <t>056</t>
+  </si>
+  <si>
+    <t>Fondo Talleres en Casas de la Cultura</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
+    <t>Fondo Jalisco de Animación Cultural</t>
+  </si>
+  <si>
+    <t>058</t>
+  </si>
+  <si>
+    <t>Programa de Apoyo a las Cultura Municipales y Comunitarias (PACMYC)</t>
   </si>
   <si>
     <t>S95_D1</t>
   </si>
   <si>
-    <t>Proyectos Estratégicos Agropecuarios, Pesqueros y Acuícolas al estilo Jalisco</t>
-  </si>
-  <si>
-    <t>015</t>
+    <t>059</t>
+  </si>
+  <si>
+    <t>Programa de Estímulo a la Creación y al Desarrollo Artístico (PECDA)</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>Proyecta Producción</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>Proyecta Traslados</t>
+  </si>
+  <si>
+    <t>062</t>
+  </si>
+  <si>
+    <t>Programa de Fomento Editorial</t>
   </si>
   <si>
     <t>S95_D3</t>
   </si>
   <si>
-    <t>Proyectos Estratégicos Agroalimentarios.</t>
-  </si>
-  <si>
-    <t>016</t>
+    <t>063</t>
+  </si>
+  <si>
+    <t>Habita la Escena</t>
+  </si>
+  <si>
+    <t>083</t>
+  </si>
+  <si>
+    <t>Fideicomiso Fondo Estatal para la Cultura y las Artes FEFCA</t>
+  </si>
+  <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>Programa ECOS, Música para la Paz</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Secretaría de Trabajo y Previsión Social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretaría de Trabajo y Previsión Social </t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empleo Temporal al Estilo Jalisco  </t>
+  </si>
+  <si>
+    <t>102</t>
   </si>
   <si>
     <t>S96_D4</t>
   </si>
   <si>
-    <t>Empedrados al estilo Jalisco</t>
-  </si>
-  <si>
-    <t>017</t>
-  </si>
-  <si>
-    <t>018</t>
+    <t xml:space="preserve">Jale seguro al estilo Jalisco </t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programa Apoyo al Empleo </t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretaría de Transporte </t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>Mujeres Conductoras Al Estilo Jalisco (LOP)</t>
+  </si>
+  <si>
+    <t>066</t>
   </si>
   <si>
     <t>S98_D1</t>
   </si>
   <si>
-    <t>Fondo Jalisco para Contingencias Agroalimentarias</t>
-  </si>
-  <si>
-    <t>019</t>
+    <t>Mujeres Conductoras Al Estilo Jalisco (ROP)</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretaría de Gestión Integral del Agua </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comisión Estatal del Agua </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nidos de LLuvia </t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretaría de Igualdad Sustantiva entre Mujeres y Hombres </t>
+  </si>
+  <si>
+    <t>068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuerza Mujeres </t>
   </si>
   <si>
     <t>S98_D2</t>
   </si>
   <si>
-    <t>Apoyo a Cooperativas de la Laguna de Cajititlán</t>
-  </si>
-  <si>
-    <t>020</t>
+    <t>069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empresarias de Alto Impacto </t>
+  </si>
+  <si>
+    <t>070</t>
+  </si>
+  <si>
+    <t>Apoyos económicos para las Hijas e Hijos de Mujeres Víctimas de Feminicidio</t>
+  </si>
+  <si>
+    <t>071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrios de Paz </t>
   </si>
   <si>
     <t>S99_D1</t>
   </si>
   <si>
-    <t>Fortalecimiento de Casas Ejidales</t>
-  </si>
-  <si>
-    <t>021</t>
-  </si>
-  <si>
-    <t>022</t>
-  </si>
-  <si>
-    <t>023</t>
+    <t>072</t>
+  </si>
+  <si>
+    <t>Estrategia Ale</t>
+  </si>
+  <si>
+    <t>073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asosiaciones por la Igualdad </t>
+  </si>
+  <si>
+    <t>096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red de Centros de Justicia para las Mujeres </t>
+  </si>
+  <si>
+    <t>074</t>
+  </si>
+  <si>
+    <t>Reglas de Operación para la Atención Especializada de Necesidades Complementarias de las Usuarias de los Centros de Justicia para las Mujeres del Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Coordinación General Estratégica de Desarrollo Social</t>
+  </si>
+  <si>
+    <t>Sistema para el Desarrollo Integral de la Familia Jalisco (DIF)</t>
+  </si>
+  <si>
+    <t>075</t>
+  </si>
+  <si>
+    <t>Programa de Atención a Grupos Prioritarios</t>
+  </si>
+  <si>
+    <t>076</t>
+  </si>
+  <si>
+    <t>Programa de Salud y Bienestar Comunitario PSBC</t>
   </si>
   <si>
     <t>S99_D2</t>
   </si>
   <si>
-    <t>024</t>
+    <t>077</t>
+  </si>
+  <si>
+    <t>Programa DIF Pilares</t>
+  </si>
+  <si>
+    <t>078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apoyos Asistenciales a Personas en Situación Prioritaria </t>
+  </si>
+  <si>
+    <t>079</t>
   </si>
   <si>
     <t>S99_B3</t>
   </si>
   <si>
-    <t>025</t>
-  </si>
-  <si>
-    <t>Agroinnovadoras y Jóvenes del campo de Jalisco</t>
-  </si>
-  <si>
-    <t>026</t>
-  </si>
-  <si>
-    <t>190</t>
+    <t>Estrategias de formación y apoyos económicos otorgados para la prevención de riesgos psicosociales y atención a la niñez</t>
+  </si>
+  <si>
+    <t>080</t>
+  </si>
+  <si>
+    <t>Acompañar la ausencia a personas familiares víctimas indirectas de una desaparición, en el Estado de Jalisco: apoyo a municipios (nombre preeliminar)</t>
+  </si>
+  <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>Apoyos asistenciales otorgados a población vulnerable. (Nombre preeliminar)</t>
   </si>
   <si>
     <t>09_190</t>
   </si>
   <si>
-    <t>Fideicomiso para Coberturas de Precios de Maíz</t>
+    <t>082</t>
   </si>
   <si>
     <t>S9C_D1</t>
   </si>
   <si>
-    <t>Fideicomiso para Coberturas de Precios de Maíz (LOP)</t>
-  </si>
-  <si>
-    <t>027</t>
-  </si>
-  <si>
-    <t>225</t>
+    <t>Acompañar la ausencia a personas familiares víctimas indirectas de una desaparición, en el Estado de Jalisco: apoyo directo (Nombre preeliminar)</t>
+  </si>
+  <si>
+    <t>Atención y Representación de Niñas, Niños y Adolescentes para la Protección y Restitución de sus Derechos en el Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>084</t>
+  </si>
+  <si>
+    <t>Fortalecer las acciones para la atención y/o reintegración de personas en situación de calle, en contexto de movilidad, tránsito, retorno o en condición de vulnerabilidad en el estado de Jalisco</t>
   </si>
   <si>
     <t>09_225</t>
   </si>
   <si>
-    <t>Agencia Estatal de Sanidad, Inocuidad y Calidad Agroalimentaria en Jalisco</t>
-  </si>
-  <si>
-    <t>028</t>
+    <t>085</t>
   </si>
   <si>
     <t>S9E_C1</t>
   </si>
   <si>
-    <t>Programa de Apoyo para el Fortalecimiento de la Inocuidad en Rastros en el Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>029</t>
+    <t>Apoyos a Personas con Discapacidad en el Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias Económicas para el Fortalecimiento de la Atención Alimentaria </t>
+  </si>
+  <si>
+    <t>087</t>
+  </si>
+  <si>
+    <t>Equipamientos para Fortalecer la Atención Alimentaria</t>
+  </si>
+  <si>
+    <t>088</t>
   </si>
   <si>
     <t>S9E_C2</t>
   </si>
   <si>
-    <t>Programa de Eliminación de Animales Positivos, Reactores, Expuestos y Sospechosos</t>
-  </si>
-  <si>
-    <t>030</t>
-  </si>
-  <si>
-    <t>031</t>
+    <t>Programa de Alimentación Escolar</t>
+  </si>
+  <si>
+    <t>089</t>
+  </si>
+  <si>
+    <t>Programa de Atención Alimentaria a Personas en Situación de Vulnerabilidad</t>
+  </si>
+  <si>
+    <t>090</t>
+  </si>
+  <si>
+    <t>Programa de Atención Alimentaria en los Primeros 1,000 Días y Primera Infancia</t>
+  </si>
+  <si>
+    <t>091</t>
+  </si>
+  <si>
+    <t>Comedores Comunitarios</t>
   </si>
   <si>
     <t>S9E_D3</t>
   </si>
   <si>
-    <t>Programa de Apoyo para la Prevención y Control del Gusano Barrenador del Ganado en el Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>032</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Medio Ambiente y Desarrollo Territorial </t>
-  </si>
-  <si>
-    <t>033</t>
-  </si>
-  <si>
-    <t>042</t>
+    <t>092</t>
+  </si>
+  <si>
+    <t>Despensas Alimentarias</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Instituto Jalisciense de la Vivienda</t>
+  </si>
+  <si>
+    <t>093</t>
+  </si>
+  <si>
+    <t>Mi Primera Renta</t>
+  </si>
+  <si>
+    <t>094</t>
   </si>
   <si>
     <t>10_042</t>
   </si>
   <si>
-    <t xml:space="preserve">O.P.D. Bosque la Primavera </t>
+    <t>Acondicionamiento de Vivienda para PCD (Recurso propio)</t>
   </si>
   <si>
     <t>S1C_D1</t>
   </si>
   <si>
-    <t>Administración y Manejo del Área de Protección de Flora y Fauna La Primavera</t>
-  </si>
-  <si>
-    <t>034</t>
+    <t>095</t>
+  </si>
+  <si>
+    <t>Mejoramiento de Vivienda</t>
+  </si>
+  <si>
+    <t>Jalisco Si Pinta (Recurso propio)</t>
   </si>
   <si>
     <t>S1C_D2</t>
   </si>
   <si>
-    <t>043</t>
-  </si>
-  <si>
     <t>S1C_D4</t>
   </si>
   <si>
-    <t>Fideicomiso para la Administración del Programa de Desarrollo Forestal del Estado de Jalisco (FIPRODEFO)</t>
-  </si>
-  <si>
     <t>10_043</t>
   </si>
   <si>
-    <t>035</t>
-  </si>
-  <si>
     <t>S1E_D6</t>
   </si>
   <si>
-    <t>Programa para el Desarrollo Forestal Sustentable del Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Secretaría del Sistema de Asistencia Social</t>
-  </si>
-  <si>
-    <t>036</t>
-  </si>
-  <si>
     <t>11_000</t>
   </si>
   <si>
-    <t xml:space="preserve">Yo Jalisco Apoyo para la Salud Mental </t>
-  </si>
-  <si>
     <t>S02_C1</t>
   </si>
   <si>
-    <t>037</t>
-  </si>
-  <si>
-    <t>Yo Jalisco, Apoyo al Transporte</t>
-  </si>
-  <si>
-    <t>038</t>
-  </si>
-  <si>
     <t>S03_C1</t>
   </si>
   <si>
-    <t>Yo Jalisco Apoyo a Personas Cuidadoras y Personas Dependientes de Cuidados</t>
-  </si>
-  <si>
-    <t>039</t>
-  </si>
-  <si>
-    <t>Yo Jalisco Apoyo para el Cuidado Infantil</t>
-  </si>
-  <si>
     <t>S03_C2</t>
   </si>
   <si>
-    <t>040</t>
-  </si>
-  <si>
-    <t>Yo Jalisco, Apoyo a Instituciones de Cuidado Infantil</t>
-  </si>
-  <si>
-    <t>041</t>
-  </si>
-  <si>
     <t>S03_C3</t>
   </si>
   <si>
-    <t xml:space="preserve">Yo Jalisco Apoyo a Jefas de Jalisco </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Listo Jalisco </t>
-  </si>
-  <si>
-    <t>S03_C4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yo Jalisco Apoyo a Asociaciones Civiles </t>
-  </si>
-  <si>
-    <t>044</t>
-  </si>
-  <si>
-    <t>Yo Jalisco, Apoyo a Nuestras Comunidades</t>
+    <t>S03_B8</t>
   </si>
   <si>
     <t>S03_C5</t>
   </si>
   <si>
-    <t>045</t>
-  </si>
-  <si>
-    <t>Yo Jalisco, Apoyo al Desarrollo Social</t>
-  </si>
-  <si>
     <t>S03_C6</t>
   </si>
   <si>
-    <t>046</t>
-  </si>
-  <si>
-    <t>Enchulemos Jalisco</t>
-  </si>
-  <si>
-    <t>047</t>
-  </si>
-  <si>
     <t>S03_A7</t>
   </si>
   <si>
-    <t>Yo Jalisco Transporte a Grupos Prioritarios</t>
-  </si>
-  <si>
-    <t>048</t>
-  </si>
-  <si>
-    <t>Yo Jalisco, Apoyo para nuestra gente</t>
-  </si>
-  <si>
     <t>S04_B1</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Secretaría de Innovación, Ciencia y Tecnológia</t>
-  </si>
-  <si>
-    <t>049</t>
-  </si>
-  <si>
-    <t>Fortalecimiento de ecosistemas regionales a través de la innovación y emprendimiento</t>
-  </si>
-  <si>
-    <t>050</t>
-  </si>
-  <si>
     <t>S04_C3</t>
   </si>
   <si>
-    <t>Fortalecimiento de la Cultura de Innovación, Ciencia y Tecnología</t>
-  </si>
-  <si>
-    <t>051</t>
-  </si>
-  <si>
-    <t>Apoyos de Educación Superior para Jóvenes LEGADO</t>
-  </si>
-  <si>
-    <t>052</t>
-  </si>
-  <si>
-    <t>Impulso y Fortalecimiento a la Educación Superior</t>
-  </si>
-  <si>
     <t>S04_B4</t>
   </si>
   <si>
-    <t>067</t>
-  </si>
-  <si>
-    <t>Consejo Estatal de Ciencia y Tecnología del Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>053</t>
-  </si>
-  <si>
-    <t>Gestión de fondos y programas de apoyo a la Ciencia, Tecnología e Innovación</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>Agencia para el Desarrollo de Industrias Creativas y Digitales del Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>054</t>
-  </si>
-  <si>
-    <t>Fondo para Proyectos de Alto Impacto a la Industria Creativa Digital</t>
-  </si>
-  <si>
     <t>S04_A5</t>
   </si>
   <si>
-    <t>055</t>
-  </si>
-  <si>
-    <t>Fondo Jalisco Creativo</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura</t>
-  </si>
-  <si>
-    <t>Secretaría de cultura</t>
-  </si>
-  <si>
-    <t>056</t>
-  </si>
-  <si>
-    <t>Fondo Talleres en Casas de la Cultura</t>
-  </si>
-  <si>
     <t>S05_B1</t>
   </si>
   <si>
-    <t>057</t>
-  </si>
-  <si>
-    <t>Fondo Jalisco de Animación Cultural</t>
-  </si>
-  <si>
-    <t>058</t>
-  </si>
-  <si>
-    <t>Programa de Apoyo a las Cultura Municipales y Comunitarias (PACMYC)</t>
-  </si>
-  <si>
     <t>S06_A1</t>
   </si>
   <si>
-    <t>059</t>
-  </si>
-  <si>
-    <t>Programa de Estímulo a la Creación y al Desarrollo Artístico (PECDA)</t>
-  </si>
-  <si>
-    <t>060</t>
-  </si>
-  <si>
-    <t>Proyecta Producción</t>
-  </si>
-  <si>
-    <t>061</t>
-  </si>
-  <si>
-    <t>Proyecta Traslados</t>
-  </si>
-  <si>
     <t>S07_A1</t>
   </si>
   <si>
-    <t>062</t>
-  </si>
-  <si>
-    <t>Programa de Fomento Editorial</t>
-  </si>
-  <si>
-    <t>063</t>
-  </si>
-  <si>
-    <t>Habita la Escena</t>
-  </si>
-  <si>
-    <t>083</t>
-  </si>
-  <si>
     <t>S07_A2</t>
   </si>
   <si>
-    <t>Fideicomiso Fondo Estatal para la Cultura y las Artes FEFCA</t>
-  </si>
-  <si>
-    <t>064</t>
-  </si>
-  <si>
-    <t>Programa ECOS, Música para la Paz</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Secretaría de Trabajo y Previsión Social</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Trabajo y Previsión Social </t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empleo Temporal al Estilo Jalisco  </t>
-  </si>
-  <si>
     <t>S08_A1</t>
   </si>
   <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jale seguro al estilo Jalisco </t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programa Apoyo al Empleo </t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Transporte </t>
-  </si>
-  <si>
     <t>S08_A2</t>
   </si>
   <si>
-    <t>065</t>
-  </si>
-  <si>
-    <t>Mujeres Conductoras Al Estilo Jalisco (LOP)</t>
-  </si>
-  <si>
-    <t>066</t>
-  </si>
-  <si>
-    <t>Mujeres Conductoras Al Estilo Jalisco (ROP)</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Gestión Integral del Agua </t>
-  </si>
-  <si>
     <t>S08_A4</t>
   </si>
   <si>
-    <t xml:space="preserve">Comisión Estatal del Agua </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nidos de LLuvia </t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Igualdad Sustantiva entre Mujeres y Hombres </t>
-  </si>
-  <si>
-    <t>068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuerza Mujeres </t>
-  </si>
-  <si>
     <t>S08_C5</t>
   </si>
   <si>
-    <t>069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empresarias de Alto Impacto </t>
-  </si>
-  <si>
-    <t>070</t>
-  </si>
-  <si>
-    <t>Apoyos económicos para las Hijas e Hijos de Mujeres Víctimas de Feminicidio</t>
-  </si>
-  <si>
     <t>S09_C3</t>
   </si>
   <si>
-    <t>071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrios de Paz </t>
-  </si>
-  <si>
-    <t>072</t>
-  </si>
-  <si>
-    <t>Estrategia Ale</t>
-  </si>
-  <si>
     <t>12_000</t>
   </si>
   <si>
-    <t>073</t>
-  </si>
-  <si>
     <t>S24_C1</t>
   </si>
   <si>
-    <t xml:space="preserve">Asosiaciones por la Igualdad </t>
-  </si>
-  <si>
-    <t>096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red de Centros de Justicia para las Mujeres </t>
-  </si>
-  <si>
-    <t>074</t>
-  </si>
-  <si>
-    <t>Reglas de Operación para la Atención Especializada de Necesidades Complementarias de las Usuarias de los Centros de Justicia para las Mujeres del Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>Coordinación General Estratégica de Desarrollo Social</t>
-  </si>
-  <si>
-    <t>Sistema para el Desarrollo Integral de la Familia Jalisco (DIF)</t>
-  </si>
-  <si>
-    <t>075</t>
-  </si>
-  <si>
     <t>S22_C2</t>
   </si>
   <si>
-    <t>Programa de Atención a Grupos Prioritarios</t>
-  </si>
-  <si>
-    <t>076</t>
-  </si>
-  <si>
-    <t>Programa de Salud y Bienestar Comunitario PSBC</t>
-  </si>
-  <si>
     <t>S21_03</t>
   </si>
   <si>
-    <t>077</t>
-  </si>
-  <si>
-    <t>Programa DIF Pilares</t>
-  </si>
-  <si>
-    <t>078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apoyos Asistenciales a Personas en Situación Prioritaria </t>
-  </si>
-  <si>
-    <t>079</t>
-  </si>
-  <si>
     <t>S21_C2</t>
   </si>
   <si>
-    <t>Estrategias de formación y apoyos económicos otorgados para la prevención de riesgos psicosociales y atención a la niñez</t>
-  </si>
-  <si>
-    <t>080</t>
-  </si>
-  <si>
-    <t>Acompañar la ausencia a personas familiares víctimas indirectas de una desaparición, en el Estado de Jalisco: apoyo a municipios (nombre preeliminar)</t>
-  </si>
-  <si>
-    <t>081</t>
-  </si>
-  <si>
-    <t>Apoyos asistenciales otorgados a población vulnerable. (Nombre preeliminar)</t>
-  </si>
-  <si>
     <t>12_067</t>
   </si>
   <si>
     <t>S2N_01</t>
   </si>
   <si>
-    <t>082</t>
-  </si>
-  <si>
-    <t>Acompañar la ausencia a personas familiares víctimas indirectas de una desaparición, en el Estado de Jalisco: apoyo directo (Nombre preeliminar)</t>
-  </si>
-  <si>
-    <t>Atención y Representación de Niñas, Niños y Adolescentes para la Protección y Restitución de sus Derechos en el Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>084</t>
-  </si>
-  <si>
     <t>S2N_02</t>
   </si>
   <si>
-    <t>Fortalecer las acciones para la atención y/o reintegración de personas en situación de calle, en contexto de movilidad, tránsito, retorno o en condición de vulnerabilidad en el estado de Jalisco</t>
-  </si>
-  <si>
-    <t>085</t>
-  </si>
-  <si>
-    <t>Apoyos a Personas con Discapacidad en el Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transferencias Económicas para el Fortalecimiento de la Atención Alimentaria </t>
-  </si>
-  <si>
     <t>S2N_03</t>
   </si>
   <si>
-    <t>087</t>
-  </si>
-  <si>
-    <t>Equipamientos para Fortalecer la Atención Alimentaria</t>
-  </si>
-  <si>
-    <t>088</t>
-  </si>
-  <si>
-    <t>Programa de Alimentación Escolar</t>
-  </si>
-  <si>
     <t>S2N_04</t>
   </si>
   <si>
-    <t>089</t>
-  </si>
-  <si>
-    <t>Programa de Atención Alimentaria a Personas en Situación de Vulnerabilidad</t>
-  </si>
-  <si>
-    <t>090</t>
-  </si>
-  <si>
-    <t>Programa de Atención Alimentaria en los Primeros 1,000 Días y Primera Infancia</t>
-  </si>
-  <si>
-    <t>091</t>
-  </si>
-  <si>
     <t>S2N_05</t>
   </si>
   <si>
-    <t>Comedores Comunitarios</t>
-  </si>
-  <si>
-    <t>092</t>
-  </si>
-  <si>
-    <t>Despensas Alimentarias</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>Instituto Jalisciense de la Vivienda</t>
-  </si>
-  <si>
     <t>12_202</t>
   </si>
   <si>
-    <t>093</t>
-  </si>
-  <si>
-    <t>Mi Primera Renta</t>
-  </si>
-  <si>
     <t>S2L_03</t>
   </si>
   <si>
-    <t>094</t>
-  </si>
-  <si>
-    <t>Acondicionamiento de Vivienda para PCD (Recurso propio)</t>
-  </si>
-  <si>
-    <t>095</t>
-  </si>
-  <si>
-    <t>Mejoramiento de Vivienda</t>
-  </si>
-  <si>
     <t>S2L_01</t>
   </si>
   <si>
-    <t>Jalisco Si Pinta (Recurso propio)</t>
-  </si>
-  <si>
     <t>13_000</t>
   </si>
   <si>
@@ -1405,7 +1405,7 @@
     <t>SE3_A2</t>
   </si>
   <si>
-    <t>SE6_B4</t>
+    <t>SE6_A4</t>
   </si>
   <si>
     <t>14_000</t>
@@ -1576,10 +1576,10 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{761b3ffd-2d8b-4228-b98e-5e34918bd52c}" providerId="google-sheets"/>
-  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{2dd59ff5-0b74-48fb-94a9-037a89012d8f}" providerId="google-sheets"/>
-  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{f18bad0b-fc62-4957-9d02-8122fbcf01b4}" providerId="google-sheets"/>
-  <x18tc:person displayName="Armando Yair Cárdenas Ávila" id="{606d8807-b65b-40ac-bfb7-2441f2256d0e}" providerId="google-sheets"/>
+  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{7b364871-8331-40bd-b527-02d9253d1f17}" providerId="google-sheets"/>
+  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{d0018b8d-5a82-4fc6-ab0a-4b7cb68e33ef}" providerId="google-sheets"/>
+  <x18tc:person displayName="Armando Yair Cárdenas Ávila" id="{114bd514-c3fa-4588-8947-87706c00e071}" providerId="google-sheets"/>
+  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{3dd7d5bc-298c-4e30-97c3-2caede612f88}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1774,7 +1774,7 @@
         <s v="S03_C1"/>
         <s v="S03_C2"/>
         <s v="S03_C3"/>
-        <s v="S03_C4"/>
+        <s v="S03_B8"/>
         <s v="S03_C5"/>
         <s v="S03_C6"/>
         <s v="S03_A7"/>
@@ -1852,7 +1852,7 @@
         <s v="SE1_A4"/>
         <s v="SE3_A1"/>
         <s v="SE3_A2"/>
-        <s v="SE6_B4"/>
+        <s v="SE6_A4"/>
         <s v="S41_C1"/>
         <s v="S41_C2"/>
         <s v="S48_01"/>
@@ -2993,31 +2993,31 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="I37" dT="2026-07-06T19:48:27.00" personId="{2dd59ff5-0b74-48fb-94a9-037a89012d8f}" id="{a1233d24-e3c5-4049-a87c-5083df344ae2}" done="1">
+  <x18tc:threadedComment ref="F85" dT="2026-06-25T21:11:19.00" personId="{3dd7d5bc-298c-4e30-97c3-2caede612f88}" id="{22233615-6a31-45f6-85e9-d87008445735}" done="1">
+    <x18tc:text xml:space="preserve">Actalmente es un Lineamiento de Operación</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="F16" dT="2026-06-25T21:15:11.00" personId="{3dd7d5bc-298c-4e30-97c3-2caede612f88}" id="{3cf0f526-fed6-4970-8110-6c1a561ba207}" done="1">
+    <x18tc:text xml:space="preserve">Actualmente cuenta con clasificación Programpatica  E</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="F16" dT="2026-06-25T21:43:13.00" personId="{3dd7d5bc-298c-4e30-97c3-2caede612f88}" id="{084650f0-ece0-464c-b53c-a4306a96e34a}" done="1">
+    <x18tc:text xml:space="preserve">Actualmente cuenta con una clasificación programática con letra E</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="I37" dT="2026-07-06T19:48:27.00" personId="{7b364871-8331-40bd-b527-02d9253d1f17}" id="{8100cc0a-5966-42ae-82f9-381e2e5b42a8}" done="1">
     <x18tc:text xml:space="preserve">A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="I121" dT="2026-08-12T23:13:36.00" personId="{606d8807-b65b-40ac-bfb7-2441f2256d0e}" id="{b23add08-53d8-4b43-a715-84ae107323f1}" done="1">
+  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{7b364871-8331-40bd-b527-02d9253d1f17}" id="{441d2b04-d373-4a9c-af6a-4de0d1fdb33e}" done="0">
+    <x18tc:text xml:space="preserve">De momento se registra el nombre del componente; a la espera de nombre de la ROP.</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="A1" dT="2026-08-03T23:05:51.00" personId="{d0018b8d-5a82-4fc6-ab0a-4b7cb68e33ef}" id="{89ccc38b-d7c7-4962-bad4-c5abec74ef0e}" done="0">
+    <x18tc:text xml:space="preserve">Le cambiaron la transversalidad</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="I121" dT="2026-08-12T23:13:36.00" personId="{114bd514-c3fa-4588-8947-87706c00e071}" id="{69da3166-d45c-4dff-ac98-f25200ba1c98}" done="1">
     <x18tc:text xml:space="preserve">Solo tiene recurso propio</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F85" dT="2026-06-25T21:11:19.00" personId="{761b3ffd-2d8b-4228-b98e-5e34918bd52c}" id="{d21d91eb-35ca-41c8-94a6-ed7c92b21572}" done="1">
-    <x18tc:text xml:space="preserve">Actalmente es un Lineamiento de Operación</x18tc:text>
-  </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{2dd59ff5-0b74-48fb-94a9-037a89012d8f}" id="{5248a60e-f01d-4dbc-8a99-ad017cf9f49b}" done="0">
-    <x18tc:text xml:space="preserve">De momento se registra el nombre del componente; a la espera de nombre de la ROP.</x18tc:text>
-  </x18tc:threadedComment>
-  <x18tc:threadedComment ref="I119" dT="2026-08-12T23:13:08.00" personId="{606d8807-b65b-40ac-bfb7-2441f2256d0e}" id="{13e6d1cf-ed57-4279-91bc-5c886f201b9b}" done="1">
+  <x18tc:threadedComment ref="I119" dT="2026-08-12T23:13:08.00" personId="{114bd514-c3fa-4588-8947-87706c00e071}" id="{a00864eb-706e-440e-8ebc-5902fb965ff6}" done="1">
     <x18tc:text xml:space="preserve">Tiene recurso propio</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-03T23:05:51.00" personId="{f18bad0b-fc62-4957-9d02-8122fbcf01b4}" id="{c7789d2a-e7d4-4a94-80c3-6be96096b045}" done="0">
-    <x18tc:text xml:space="preserve">Le cambiaron la transversalidad</x18tc:text>
-  </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F16" dT="2026-06-25T21:15:11.00" personId="{761b3ffd-2d8b-4228-b98e-5e34918bd52c}" id="{dd6ac2d0-9edd-46b4-b0ef-33f174cf3d44}" done="1">
-    <x18tc:text xml:space="preserve">Actualmente cuenta con clasificación Programpatica  E</x18tc:text>
-  </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F16" dT="2026-06-25T21:43:13.00" personId="{761b3ffd-2d8b-4228-b98e-5e34918bd52c}" id="{c743d331-7ec0-4487-86f4-79a5044ac75e}" done="1">
-    <x18tc:text xml:space="preserve">Actualmente cuenta con una clasificación programática con letra E</x18tc:text>
-  </x18tc:threadedComment>
-  <x18tc:threadedComment ref="H33" dT="2026-09-15T18:45:08.00" personId="{2dd59ff5-0b74-48fb-94a9-037a89012d8f}" id="{3ce3c437-15dd-4a3f-8f1c-a331284ffb19}" done="0">
+  <x18tc:threadedComment ref="H33" dT="2026-09-15T18:45:08.00" personId="{7b364871-8331-40bd-b527-02d9253d1f17}" id="{4e3e344e-aaf2-4972-b3a3-c64713db101d}" done="0">
     <x18tc:text xml:space="preserve">Se eliminó componente.</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -3416,7 +3416,7 @@
         <v>ROP</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>18</v>
@@ -3462,17 +3462,17 @@
         <v>13</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G8" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>19</v>
@@ -3515,17 +3515,17 @@
         <v>13</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G9" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>19</v>
@@ -3568,17 +3568,17 @@
         <v>13</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G10" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>19</v>
@@ -3621,17 +3621,17 @@
         <v>13</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G11" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>19</v>
@@ -3665,13 +3665,13 @@
         <v>13</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>16</v>
@@ -3681,10 +3681,10 @@
         <v>ROP</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>19</v>
@@ -3718,13 +3718,13 @@
         <v>13</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>16</v>
@@ -3734,10 +3734,10 @@
         <v>ROP</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>19</v>
@@ -3771,13 +3771,13 @@
         <v>13</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>16</v>
@@ -3787,10 +3787,10 @@
         <v>ROP</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>19</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>54</v>
@@ -3827,10 +3827,10 @@
         <v>55</v>
       </c>
       <c r="D15" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>16</v>
@@ -3840,10 +3840,10 @@
         <v>ROP</v>
       </c>
       <c r="H15" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I15" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>19</v>
@@ -3871,7 +3871,7 @@
     </row>
     <row r="16">
       <c r="A16" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>54</v>
@@ -3880,23 +3880,23 @@
         <v>55</v>
       </c>
       <c r="D16" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>58</v>
-      </c>
       <c r="F16" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G16" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>19</v>
@@ -3924,19 +3924,19 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>16</v>
@@ -3946,10 +3946,10 @@
         <v>ROP</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>19</v>
@@ -3977,19 +3977,19 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>16</v>
@@ -3999,10 +3999,10 @@
         <v>ROP</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>19</v>
@@ -4030,19 +4030,19 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>16</v>
@@ -4052,10 +4052,10 @@
         <v>ROP</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>19</v>
@@ -4083,32 +4083,32 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G20" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>19</v>
@@ -4136,19 +4136,19 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>16</v>
@@ -4158,10 +4158,10 @@
         <v>ROP</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>19</v>
@@ -4189,32 +4189,32 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>92</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G22" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>19</v>
@@ -4242,19 +4242,19 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>92</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>16</v>
@@ -4264,10 +4264,10 @@
         <v>ROP</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>99</v>
+        <v>178</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>19</v>
@@ -4295,19 +4295,19 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>16</v>
@@ -4317,10 +4317,10 @@
         <v>ROP</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>107</v>
+        <v>187</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>19</v>
@@ -4348,19 +4348,19 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>16</v>
@@ -4370,10 +4370,10 @@
         <v>ROP</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>19</v>
@@ -4401,19 +4401,19 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>16</v>
@@ -4423,10 +4423,10 @@
         <v>ROP</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>112</v>
+        <v>207</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>19</v>
@@ -4454,19 +4454,19 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>16</v>
@@ -4476,10 +4476,10 @@
         <v>ROP</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>115</v>
+        <v>214</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>19</v>
@@ -4507,32 +4507,32 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G28" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>118</v>
+        <v>223</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>19</v>
@@ -4560,32 +4560,32 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G29" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>121</v>
+        <v>236</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>19</v>
@@ -4613,19 +4613,19 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>16</v>
@@ -4635,10 +4635,10 @@
         <v>ROP</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>125</v>
+        <v>245</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>19</v>
@@ -4666,19 +4666,19 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>16</v>
@@ -4688,10 +4688,10 @@
         <v>ROP</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>128</v>
+        <v>255</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>19</v>
@@ -4719,19 +4719,19 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>16</v>
@@ -4741,10 +4741,10 @@
         <v>ROP</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>131</v>
+        <v>262</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>19</v>
@@ -4772,19 +4772,19 @@
     </row>
     <row r="33">
       <c r="A33" s="10" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>16</v>
@@ -4794,10 +4794,10 @@
         <v>ROP</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>136</v>
+        <v>278</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>19</v>
@@ -4825,19 +4825,19 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>16</v>
@@ -4847,10 +4847,10 @@
         <v>ROP</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>138</v>
+        <v>284</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="J34" s="5" t="s">
         <v>19</v>
@@ -4878,32 +4878,32 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>143</v>
+        <v>290</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G35" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>145</v>
+        <v>292</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="J35" s="5" t="s">
         <v>19</v>
@@ -4931,32 +4931,32 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>149</v>
+        <v>297</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G36" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>152</v>
+        <v>299</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="J36" s="5" t="s">
         <v>19</v>
@@ -4984,19 +4984,19 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>149</v>
+        <v>297</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>16</v>
@@ -5006,10 +5006,10 @@
         <v>ROP</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>155</v>
+        <v>306</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="J37" s="5" t="s">
         <v>19</v>
@@ -5037,32 +5037,32 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>149</v>
+        <v>297</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G38" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="J38" s="5" t="s">
         <v>19</v>
@@ -5090,19 +5090,19 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>166</v>
+        <v>322</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>16</v>
@@ -5112,10 +5112,10 @@
         <v>ROP</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>168</v>
+        <v>324</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="J39" s="5" t="s">
         <v>19</v>
@@ -5143,19 +5143,19 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>166</v>
+        <v>322</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>16</v>
@@ -5165,10 +5165,10 @@
         <v>ROP</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>171</v>
+        <v>328</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="J40" s="5" t="s">
         <v>19</v>
@@ -5196,19 +5196,19 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>166</v>
+        <v>322</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>16</v>
@@ -5218,10 +5218,10 @@
         <v>ROP</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>173</v>
+        <v>329</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="J41" s="5" t="s">
         <v>19</v>
@@ -5249,19 +5249,19 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>175</v>
+        <v>330</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>16</v>
@@ -5271,10 +5271,10 @@
         <v>ROP</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>177</v>
+        <v>331</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="J42" s="5" t="s">
         <v>19</v>
@@ -5302,32 +5302,32 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G43" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>184</v>
+        <v>333</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="J43" s="5" t="s">
         <v>19</v>
@@ -5355,19 +5355,19 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>16</v>
@@ -5377,10 +5377,10 @@
         <v>ROP</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>188</v>
+        <v>334</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="J44" s="5" t="s">
         <v>19</v>
@@ -5408,19 +5408,19 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>16</v>
@@ -5430,10 +5430,10 @@
         <v>ROP</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>192</v>
+        <v>335</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="J45" s="5" t="s">
         <v>19</v>
@@ -5461,19 +5461,19 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>16</v>
@@ -5483,10 +5483,10 @@
         <v>ROP</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>196</v>
+        <v>336</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="J46" s="5" t="s">
         <v>19</v>
@@ -5514,19 +5514,19 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>16</v>
@@ -5536,10 +5536,10 @@
         <v>ROP</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>199</v>
+        <v>337</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="J47" s="5" t="s">
         <v>19</v>
@@ -5567,19 +5567,19 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>16</v>
@@ -5589,10 +5589,10 @@
         <v>ROP</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>203</v>
+        <v>338</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="J48" s="5" t="s">
         <v>19</v>
@@ -5620,19 +5620,19 @@
     </row>
     <row r="49">
       <c r="A49" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>16</v>
@@ -5642,10 +5642,10 @@
         <v>ROP</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>206</v>
+        <v>339</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="J49" s="5" t="s">
         <v>19</v>
@@ -5673,19 +5673,19 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>16</v>
@@ -5695,10 +5695,10 @@
         <v>ROP</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>210</v>
+        <v>340</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="J50" s="5" t="s">
         <v>19</v>
@@ -5726,19 +5726,19 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>16</v>
@@ -5748,10 +5748,10 @@
         <v>ROP</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>214</v>
+        <v>341</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>19</v>
@@ -5779,19 +5779,19 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>16</v>
@@ -5801,10 +5801,10 @@
         <v>ROP</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>220</v>
+        <v>342</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="J52" s="5" t="s">
         <v>19</v>
@@ -5832,19 +5832,19 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>16</v>
@@ -5854,10 +5854,10 @@
         <v>ROP</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>226</v>
+        <v>343</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="J53" s="5" t="s">
         <v>19</v>
@@ -5885,32 +5885,32 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G54" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>235</v>
+        <v>344</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="J54" s="5" t="s">
         <v>19</v>
@@ -5938,19 +5938,19 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>16</v>
@@ -5960,10 +5960,10 @@
         <v>ROP</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>243</v>
+        <v>345</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="J55" s="5" t="s">
         <v>19</v>
@@ -5991,19 +5991,19 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>16</v>
@@ -6013,10 +6013,10 @@
         <v>ROP</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>248</v>
+        <v>346</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="J56" s="5" t="s">
         <v>19</v>
@@ -6044,32 +6044,32 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G57" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>255</v>
+        <v>347</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="J57" s="5" t="s">
         <v>19</v>
@@ -6097,32 +6097,32 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G58" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>261</v>
+        <v>348</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="J58" s="5" t="s">
         <v>19</v>
@@ -6150,32 +6150,32 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G59" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>270</v>
+        <v>349</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>19</v>
@@ -6203,19 +6203,19 @@
     </row>
     <row r="60">
       <c r="A60" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>16</v>
@@ -6225,10 +6225,10 @@
         <v>ROP</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>277</v>
+        <v>350</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="J60" s="5" t="s">
         <v>19</v>
@@ -6256,32 +6256,32 @@
     </row>
     <row r="61">
       <c r="A61" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G61" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>284</v>
+        <v>351</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="J61" s="5" t="s">
         <v>19</v>
@@ -6309,32 +6309,32 @@
     </row>
     <row r="62">
       <c r="A62" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G62" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="J62" s="5" t="s">
         <v>19</v>
@@ -6362,19 +6362,19 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>16</v>
@@ -6384,10 +6384,10 @@
         <v>ROP</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>296</v>
+        <v>353</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="J63" s="5" t="s">
         <v>19</v>
@@ -6415,32 +6415,32 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>301</v>
+        <v>354</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G64" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>303</v>
+        <v>355</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>218</v>
+        <v>184</v>
       </c>
       <c r="J64" s="5" t="s">
         <v>19</v>
@@ -6468,32 +6468,32 @@
     </row>
     <row r="65">
       <c r="A65" s="5" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>301</v>
+        <v>354</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G65" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>313</v>
+        <v>356</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>19</v>
@@ -6521,32 +6521,32 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>301</v>
+        <v>354</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G66" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>19</v>
@@ -6574,32 +6574,32 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>301</v>
+        <v>354</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G67" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>323</v>
+        <v>358</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>19</v>
@@ -6627,19 +6627,19 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>16</v>
@@ -6649,10 +6649,10 @@
         <v>ROP</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>19</v>
@@ -6680,19 +6680,19 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>16</v>
@@ -6702,10 +6702,10 @@
         <v>ROP</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>19</v>
@@ -6733,19 +6733,19 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>16</v>
@@ -6755,10 +6755,10 @@
         <v>ROP</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>19</v>
@@ -6786,19 +6786,19 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>16</v>
@@ -6808,10 +6808,10 @@
         <v>ROP</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>19</v>
@@ -6839,19 +6839,19 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>16</v>
@@ -6861,10 +6861,10 @@
         <v>ROP</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>19</v>
@@ -6892,19 +6892,19 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>16</v>
@@ -6914,10 +6914,10 @@
         <v>ROP</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>234</v>
+        <v>201</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>19</v>
@@ -6945,32 +6945,32 @@
     </row>
     <row r="74">
       <c r="A74" s="5" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G74" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>19</v>
@@ -6998,10 +6998,10 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>14</v>
@@ -7010,10 +7010,10 @@
         <v>368</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G75" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7023,7 +7023,7 @@
         <v>369</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>19</v>
@@ -7051,10 +7051,10 @@
     </row>
     <row r="76">
       <c r="A76" s="5" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>14</v>
@@ -7063,10 +7063,10 @@
         <v>368</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G76" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7076,7 +7076,7 @@
         <v>370</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>19</v>
@@ -7104,10 +7104,10 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>14</v>
@@ -7116,7 +7116,7 @@
         <v>368</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>16</v>
@@ -7129,7 +7129,7 @@
         <v>371</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>372</v>
@@ -7157,10 +7157,10 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>14</v>
@@ -7169,7 +7169,7 @@
         <v>368</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>16</v>
@@ -7182,7 +7182,7 @@
         <v>373</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>372</v>
@@ -7210,10 +7210,10 @@
     </row>
     <row r="79">
       <c r="A79" s="5" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>14</v>
@@ -7222,7 +7222,7 @@
         <v>368</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>16</v>
@@ -7235,7 +7235,7 @@
         <v>374</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>19</v>
@@ -7263,10 +7263,10 @@
     </row>
     <row r="80">
       <c r="A80" s="5" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>14</v>
@@ -7275,7 +7275,7 @@
         <v>368</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>16</v>
@@ -7288,7 +7288,7 @@
         <v>375</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>254</v>
+        <v>220</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>19</v>
@@ -7316,10 +7316,10 @@
     </row>
     <row r="81">
       <c r="A81" s="5" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>14</v>
@@ -7328,7 +7328,7 @@
         <v>368</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>16</v>
@@ -7341,7 +7341,7 @@
         <v>376</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>257</v>
+        <v>222</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>19</v>
@@ -7369,10 +7369,10 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>14</v>
@@ -7381,7 +7381,7 @@
         <v>368</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>16</v>
@@ -7394,7 +7394,7 @@
         <v>377</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>259</v>
+        <v>225</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>19</v>
@@ -7422,22 +7422,22 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>260</v>
+        <v>226</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>378</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>262</v>
+        <v>227</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G83" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7447,7 +7447,7 @@
         <v>379</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>19</v>
@@ -7475,22 +7475,22 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>260</v>
+        <v>226</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>378</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>262</v>
+        <v>227</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G84" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7500,7 +7500,7 @@
         <v>380</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="J84" s="5" t="s">
         <v>19</v>
@@ -7528,10 +7528,10 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="s">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>276</v>
+        <v>241</v>
       </c>
       <c r="C85" s="9" t="s">
         <v>14</v>
@@ -7540,10 +7540,10 @@
         <v>381</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>276</v>
+        <v>241</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G85" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7553,7 +7553,7 @@
         <v>382</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="J85" s="5" t="s">
         <v>19</v>
@@ -7581,10 +7581,10 @@
     </row>
     <row r="86">
       <c r="A86" s="5" t="s">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>276</v>
+        <v>241</v>
       </c>
       <c r="C86" s="9" t="s">
         <v>14</v>
@@ -7593,7 +7593,7 @@
         <v>381</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>276</v>
+        <v>241</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>16</v>
@@ -7606,7 +7606,7 @@
         <v>383</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>281</v>
+        <v>246</v>
       </c>
       <c r="J86" s="5" t="s">
         <v>19</v>
@@ -7634,19 +7634,19 @@
     </row>
     <row r="87">
       <c r="A87" s="5" t="s">
-        <v>282</v>
+        <v>247</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>384</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>16</v>
@@ -7659,7 +7659,7 @@
         <v>385</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="J87" s="5" t="s">
         <v>19</v>
@@ -7687,19 +7687,19 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="s">
-        <v>282</v>
+        <v>247</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>384</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>16</v>
@@ -7712,7 +7712,7 @@
         <v>386</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>19</v>
@@ -7740,10 +7740,10 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="C89" s="9" t="s">
         <v>14</v>
@@ -7752,7 +7752,7 @@
         <v>387</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>16</v>
@@ -7765,7 +7765,7 @@
         <v>388</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="J89" s="5" t="s">
         <v>19</v>
@@ -7793,10 +7793,10 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="C90" s="9" t="s">
         <v>14</v>
@@ -7805,7 +7805,7 @@
         <v>387</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>16</v>
@@ -7818,7 +7818,7 @@
         <v>389</v>
       </c>
       <c r="I90" s="5" t="s">
-        <v>293</v>
+        <v>257</v>
       </c>
       <c r="J90" s="5" t="s">
         <v>19</v>
@@ -7846,10 +7846,10 @@
     </row>
     <row r="91">
       <c r="A91" s="5" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="C91" s="9" t="s">
         <v>14</v>
@@ -7858,7 +7858,7 @@
         <v>387</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>16</v>
@@ -7871,7 +7871,7 @@
         <v>390</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>295</v>
+        <v>259</v>
       </c>
       <c r="J91" s="5" t="s">
         <v>19</v>
@@ -7899,10 +7899,10 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="C92" s="9" t="s">
         <v>14</v>
@@ -7911,10 +7911,10 @@
         <v>387</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G92" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7924,7 +7924,7 @@
         <v>391</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>298</v>
+        <v>261</v>
       </c>
       <c r="J92" s="5" t="s">
         <v>19</v>
@@ -7952,10 +7952,10 @@
     </row>
     <row r="93">
       <c r="A93" s="5" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="C93" s="9" t="s">
         <v>14</v>
@@ -7964,10 +7964,10 @@
         <v>387</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G93" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7977,7 +7977,7 @@
         <v>392</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="J93" s="5" t="s">
         <v>19</v>
@@ -8005,10 +8005,10 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="C94" s="9" t="s">
         <v>14</v>
@@ -8017,10 +8017,10 @@
         <v>387</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G94" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8030,7 +8030,7 @@
         <v>393</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>304</v>
+        <v>266</v>
       </c>
       <c r="J94" s="5" t="s">
         <v>19</v>
@@ -8058,19 +8058,19 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>305</v>
+        <v>267</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>394</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>306</v>
+        <v>268</v>
       </c>
       <c r="F95" s="5" t="s">
         <v>16</v>
@@ -8083,7 +8083,7 @@
         <v>395</v>
       </c>
       <c r="I95" s="5" t="s">
-        <v>308</v>
+        <v>270</v>
       </c>
       <c r="J95" s="5" t="s">
         <v>396</v>
@@ -8111,19 +8111,19 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F96" s="5" t="s">
         <v>16</v>
@@ -8136,7 +8136,7 @@
         <v>398</v>
       </c>
       <c r="I96" s="5" t="s">
-        <v>314</v>
+        <v>275</v>
       </c>
       <c r="J96" s="5" t="s">
         <v>372</v>
@@ -8164,19 +8164,19 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>16</v>
@@ -8189,7 +8189,7 @@
         <v>399</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>314</v>
+        <v>275</v>
       </c>
       <c r="J97" s="5" t="s">
         <v>372</v>
@@ -8217,19 +8217,19 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>16</v>
@@ -8242,7 +8242,7 @@
         <v>400</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>314</v>
+        <v>275</v>
       </c>
       <c r="J98" s="5" t="s">
         <v>372</v>
@@ -8270,19 +8270,19 @@
     </row>
     <row r="99">
       <c r="A99" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F99" s="5" t="s">
         <v>16</v>
@@ -8295,7 +8295,7 @@
         <v>401</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>314</v>
+        <v>275</v>
       </c>
       <c r="J99" s="5" t="s">
         <v>372</v>
@@ -8323,19 +8323,19 @@
     </row>
     <row r="100">
       <c r="A100" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F100" s="5" t="s">
         <v>16</v>
@@ -8348,7 +8348,7 @@
         <v>402</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>316</v>
+        <v>277</v>
       </c>
       <c r="J100" s="5" t="s">
         <v>372</v>
@@ -8376,19 +8376,19 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>16</v>
@@ -8401,7 +8401,7 @@
         <v>403</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>316</v>
+        <v>277</v>
       </c>
       <c r="J101" s="5" t="s">
         <v>372</v>
@@ -8429,19 +8429,19 @@
     </row>
     <row r="102">
       <c r="A102" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>16</v>
@@ -8454,7 +8454,7 @@
         <v>404</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>319</v>
+        <v>280</v>
       </c>
       <c r="J102" s="5" t="s">
         <v>372</v>
@@ -8482,22 +8482,22 @@
     </row>
     <row r="103">
       <c r="A103" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G103" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8507,7 +8507,7 @@
         <v>405</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>321</v>
+        <v>282</v>
       </c>
       <c r="J103" s="5" t="s">
         <v>19</v>
@@ -8535,22 +8535,22 @@
     </row>
     <row r="104">
       <c r="A104" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G104" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8560,7 +8560,7 @@
         <v>406</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>324</v>
+        <v>285</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>19</v>
@@ -8588,22 +8588,22 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G105" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8613,7 +8613,7 @@
         <v>407</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>326</v>
+        <v>287</v>
       </c>
       <c r="J105" s="5" t="s">
         <v>19</v>
@@ -8641,19 +8641,19 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F106" s="5" t="s">
         <v>16</v>
@@ -8666,7 +8666,7 @@
         <v>408</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>328</v>
+        <v>289</v>
       </c>
       <c r="J106" s="5" t="s">
         <v>19</v>
@@ -8694,19 +8694,19 @@
     </row>
     <row r="107">
       <c r="A107" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>16</v>
@@ -8719,7 +8719,7 @@
         <v>409</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>332</v>
+        <v>293</v>
       </c>
       <c r="J107" s="5" t="s">
         <v>19</v>
@@ -8747,22 +8747,22 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G108" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8772,7 +8772,7 @@
         <v>410</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>333</v>
+        <v>294</v>
       </c>
       <c r="J108" s="5" t="s">
         <v>19</v>
@@ -8800,22 +8800,22 @@
     </row>
     <row r="109" ht="60.0" customHeight="1">
       <c r="A109" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G109" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8825,7 +8825,7 @@
         <v>411</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>336</v>
+        <v>296</v>
       </c>
       <c r="J109" s="5" t="s">
         <v>19</v>
@@ -8853,19 +8853,19 @@
     </row>
     <row r="110">
       <c r="A110" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F110" s="5" t="s">
         <v>16</v>
@@ -8878,7 +8878,7 @@
         <v>412</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>338</v>
+        <v>300</v>
       </c>
       <c r="J110" s="5" t="s">
         <v>19</v>
@@ -8906,22 +8906,22 @@
     </row>
     <row r="111">
       <c r="A111" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G111" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8931,7 +8931,7 @@
         <v>413</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>340</v>
+        <v>302</v>
       </c>
       <c r="J111" s="5" t="s">
         <v>19</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G112" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8984,7 +8984,7 @@
         <v>414</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>343</v>
+        <v>304</v>
       </c>
       <c r="J112" s="5" t="s">
         <v>19</v>
@@ -9012,19 +9012,19 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>16</v>
@@ -9037,7 +9037,7 @@
         <v>415</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>345</v>
+        <v>307</v>
       </c>
       <c r="J113" s="5" t="s">
         <v>372</v>
@@ -9065,19 +9065,19 @@
     </row>
     <row r="114">
       <c r="A114" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>16</v>
@@ -9090,7 +9090,7 @@
         <v>416</v>
       </c>
       <c r="I114" s="5" t="s">
-        <v>348</v>
+        <v>309</v>
       </c>
       <c r="J114" s="5" t="s">
         <v>372</v>
@@ -9118,19 +9118,19 @@
     </row>
     <row r="115">
       <c r="A115" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F115" s="5" t="s">
         <v>16</v>
@@ -9143,7 +9143,7 @@
         <v>417</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>350</v>
+        <v>311</v>
       </c>
       <c r="J115" s="5" t="s">
         <v>372</v>
@@ -9171,22 +9171,22 @@
     </row>
     <row r="116">
       <c r="A116" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G116" s="5" t="str">
         <f t="shared" si="1"/>
@@ -9196,7 +9196,7 @@
         <v>418</v>
       </c>
       <c r="I116" s="5" t="s">
-        <v>353</v>
+        <v>313</v>
       </c>
       <c r="J116" s="5" t="s">
         <v>19</v>
@@ -9224,22 +9224,22 @@
     </row>
     <row r="117">
       <c r="A117" s="5" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G117" s="5" t="str">
         <f t="shared" si="1"/>
@@ -9249,7 +9249,7 @@
         <v>419</v>
       </c>
       <c r="I117" s="5" t="s">
-        <v>355</v>
+        <v>316</v>
       </c>
       <c r="J117" s="5" t="s">
         <v>19</v>
@@ -9277,10 +9277,10 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="s">
-        <v>356</v>
+        <v>317</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>14</v>
@@ -9289,7 +9289,7 @@
         <v>420</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>16</v>
@@ -9302,7 +9302,7 @@
         <v>421</v>
       </c>
       <c r="I118" s="5" t="s">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="J118" s="5" t="s">
         <v>19</v>
@@ -9330,10 +9330,10 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="s">
-        <v>356</v>
+        <v>317</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>14</v>
@@ -9342,7 +9342,7 @@
         <v>420</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>16</v>
@@ -9355,7 +9355,7 @@
         <v>422</v>
       </c>
       <c r="I119" s="5" t="s">
-        <v>363</v>
+        <v>323</v>
       </c>
       <c r="J119" s="5" t="s">
         <v>19</v>
@@ -9383,10 +9383,10 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="s">
-        <v>356</v>
+        <v>317</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>14</v>
@@ -9395,7 +9395,7 @@
         <v>420</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F120" s="5" t="s">
         <v>16</v>
@@ -9408,7 +9408,7 @@
         <v>423</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>365</v>
+        <v>326</v>
       </c>
       <c r="J120" s="5" t="s">
         <v>19</v>
@@ -9436,10 +9436,10 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="s">
-        <v>356</v>
+        <v>317</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>14</v>
@@ -9448,10 +9448,10 @@
         <v>420</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G121" s="5" t="str">
         <f t="shared" si="1"/>
@@ -9461,7 +9461,7 @@
         <v>424</v>
       </c>
       <c r="I121" s="5" t="s">
-        <v>367</v>
+        <v>327</v>
       </c>
       <c r="J121" s="5" t="s">
         <v>19</v>
@@ -9489,10 +9489,10 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>14</v>
@@ -9501,7 +9501,7 @@
         <v>425</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>16</v>
@@ -9514,7 +9514,7 @@
         <v>426</v>
       </c>
       <c r="I122" s="5" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="J122" s="5" t="s">
         <v>396</v>
@@ -9542,10 +9542,10 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>14</v>
@@ -9554,7 +9554,7 @@
         <v>425</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>16</v>
@@ -9567,7 +9567,7 @@
         <v>427</v>
       </c>
       <c r="I123" s="5" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="J123" s="5" t="s">
         <v>396</v>
@@ -9595,10 +9595,10 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>14</v>
@@ -9607,7 +9607,7 @@
         <v>425</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>16</v>
@@ -9620,7 +9620,7 @@
         <v>428</v>
       </c>
       <c r="I124" s="5" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="J124" s="5" t="s">
         <v>396</v>
@@ -9648,10 +9648,10 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>14</v>
@@ -9660,7 +9660,7 @@
         <v>425</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>16</v>
@@ -9673,7 +9673,7 @@
         <v>429</v>
       </c>
       <c r="I125" s="5" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="J125" s="5" t="s">
         <v>396</v>
@@ -9701,10 +9701,10 @@
     </row>
     <row r="126">
       <c r="A126" s="5" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>266</v>
+        <v>231</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>14</v>
@@ -9713,7 +9713,7 @@
         <v>430</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>16</v>
@@ -9726,7 +9726,7 @@
         <v>431</v>
       </c>
       <c r="I126" s="5" t="s">
-        <v>269</v>
+        <v>234</v>
       </c>
       <c r="J126" s="5" t="s">
         <v>396</v>
@@ -9754,10 +9754,10 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>266</v>
+        <v>231</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>14</v>
@@ -9766,7 +9766,7 @@
         <v>430</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>16</v>
@@ -9779,7 +9779,7 @@
         <v>432</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>269</v>
+        <v>234</v>
       </c>
       <c r="J127" s="5" t="s">
         <v>396</v>
@@ -9807,10 +9807,10 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>266</v>
+        <v>231</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>14</v>
@@ -9819,7 +9819,7 @@
         <v>430</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>16</v>
@@ -9832,7 +9832,7 @@
         <v>433</v>
       </c>
       <c r="I128" s="5" t="s">
-        <v>272</v>
+        <v>237</v>
       </c>
       <c r="J128" s="5" t="s">
         <v>396</v>
@@ -9860,10 +9860,10 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>266</v>
+        <v>231</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>14</v>
@@ -9872,7 +9872,7 @@
         <v>430</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>16</v>
@@ -9885,7 +9885,7 @@
         <v>434</v>
       </c>
       <c r="I129" s="5" t="s">
-        <v>272</v>
+        <v>237</v>
       </c>
       <c r="J129" s="5" t="s">
         <v>396</v>
@@ -9913,10 +9913,10 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>266</v>
+        <v>231</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>14</v>
@@ -9925,7 +9925,7 @@
         <v>430</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>16</v>
@@ -9938,7 +9938,7 @@
         <v>435</v>
       </c>
       <c r="I130" s="5" t="s">
-        <v>272</v>
+        <v>237</v>
       </c>
       <c r="J130" s="5" t="s">
         <v>396</v>
@@ -9966,10 +9966,10 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>266</v>
+        <v>231</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>14</v>
@@ -9978,7 +9978,7 @@
         <v>430</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>16</v>
@@ -9991,7 +9991,7 @@
         <v>436</v>
       </c>
       <c r="I131" s="5" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="J131" s="5" t="s">
         <v>396</v>
@@ -10019,10 +10019,10 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>266</v>
+        <v>231</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>14</v>
@@ -10031,7 +10031,7 @@
         <v>430</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>16</v>
@@ -10044,7 +10044,7 @@
         <v>437</v>
       </c>
       <c r="I132" s="5" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="J132" s="5" t="s">
         <v>396</v>
@@ -10072,10 +10072,10 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>266</v>
+        <v>231</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>14</v>
@@ -10084,7 +10084,7 @@
         <v>430</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>16</v>
@@ -10097,7 +10097,7 @@
         <v>438</v>
       </c>
       <c r="I133" s="5" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="J133" s="5" t="s">
         <v>396</v>
@@ -10125,19 +10125,19 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>143</v>
+        <v>290</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>16</v>

--- a/Catálogo ROP-LOP 2027.xlsx
+++ b/Catálogo ROP-LOP 2027.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Tabla dinámica 2" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Hoja 1'!$A$1:$K$134</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Hoja 1'!$A$1:$K$136</definedName>
   </definedNames>
   <calcPr/>
   <pivotCaches>
@@ -19,18 +19,65 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={084650f0-ece0-464c-b53c-a4306a96e34a}</author>
-    <author>tc={22233615-6a31-45f6-85e9-d87008445735}</author>
-    <author>tc={3cf0f526-fed6-4970-8110-6c1a561ba207}</author>
-    <author>tc={441d2b04-d373-4a9c-af6a-4de0d1fdb33e}</author>
-    <author>tc={4e3e344e-aaf2-4972-b3a3-c64713db101d}</author>
-    <author>tc={69da3166-d45c-4dff-ac98-f25200ba1c98}</author>
-    <author>tc={8100cc0a-5966-42ae-82f9-381e2e5b42a8}</author>
-    <author>tc={89ccc38b-d7c7-4962-bad4-c5abec74ef0e}</author>
-    <author>tc={a00864eb-706e-440e-8ebc-5902fb965ff6}</author>
+    <author>tc={5298d5ab-eb5a-40c5-a769-325a49962664}</author>
+    <author>tc={57366feb-1f43-4800-9540-a1243fb02836}</author>
+    <author>tc={7bd4eed0-cf44-4594-bfa5-0a45225cbe5d}</author>
+    <author>tc={9a62354d-f2a3-4594-b6b3-01b8d11f20f1}</author>
+    <author>tc={a204895e-58cf-4d20-af7f-93bb9067096f}</author>
+    <author>tc={a94b4d88-de05-4cad-88dc-c7ff14a36a20}</author>
+    <author>tc={b31cd7ed-42a8-45af-acfe-c2ec20c8a2b6}</author>
+    <author>tc={b47461d1-de0e-47d4-b614-4d8bb7e9ec82}</author>
+    <author>tc={cc49baf0-5f50-4e72-880a-13eb15cdcc18}</author>
+    <author>tc={df2ba1e2-2b7d-45cd-9d5b-74290b0746d2}</author>
+    <author>tc={ff932e4d-2f32-4ebb-bd88-696a66e50400}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{084650f0-ece0-464c-b53c-a4306a96e34a}" ref="F16">
+    <comment authorId="0" xr:uid="{5298d5ab-eb5a-40c5-a769-325a49962664}" ref="F16">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Actualmente cuenta con clasificación Programpatica  E
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{57366feb-1f43-4800-9540-a1243fb02836}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	De momento se registra el nombre del componente; a la espera de nombre de la ROP.
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{7bd4eed0-cf44-4594-bfa5-0a45225cbe5d}" ref="I37">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{9a62354d-f2a3-4594-b6b3-01b8d11f20f1}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Le cambiaron la transversalidad
+</t>
+      </text>
+    </comment>
+    <comment authorId="4" xr:uid="{a204895e-58cf-4d20-af7f-93bb9067096f}" ref="H48">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Componente anterior (cambió de transversalidad)
+</t>
+      </text>
+    </comment>
+    <comment authorId="5" xr:uid="{a94b4d88-de05-4cad-88dc-c7ff14a36a20}" ref="F16">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -39,7 +86,25 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{22233615-6a31-45f6-85e9-d87008445735}" ref="F85">
+    <comment authorId="6" xr:uid="{b31cd7ed-42a8-45af-acfe-c2ec20c8a2b6}" ref="I120">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Tiene recurso propio
+</t>
+      </text>
+    </comment>
+    <comment authorId="7" xr:uid="{b47461d1-de0e-47d4-b614-4d8bb7e9ec82}" ref="H33">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Se eliminó componente.
+</t>
+      </text>
+    </comment>
+    <comment authorId="8" xr:uid="{cc49baf0-5f50-4e72-880a-13eb15cdcc18}" ref="F86">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -48,34 +113,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{3cf0f526-fed6-4970-8110-6c1a561ba207}" ref="F16">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Actualmente cuenta con clasificación Programpatica  E
-</t>
-      </text>
-    </comment>
-    <comment authorId="3" xr:uid="{441d2b04-d373-4a9c-af6a-4de0d1fdb33e}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	De momento se registra el nombre del componente; a la espera de nombre de la ROP.
-</t>
-      </text>
-    </comment>
-    <comment authorId="4" xr:uid="{4e3e344e-aaf2-4972-b3a3-c64713db101d}" ref="H33">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Se eliminó componente.
-</t>
-      </text>
-    </comment>
-    <comment authorId="5" xr:uid="{69da3166-d45c-4dff-ac98-f25200ba1c98}" ref="I121">
+    <comment authorId="9" xr:uid="{df2ba1e2-2b7d-45cd-9d5b-74290b0746d2}" ref="I122">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -84,30 +122,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="6" xr:uid="{8100cc0a-5966-42ae-82f9-381e2e5b42a8}" ref="I37">
+    <comment authorId="10" xr:uid="{ff932e4d-2f32-4ebb-bd88-696a66e50400}" ref="H127">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.
-</t>
-      </text>
-    </comment>
-    <comment authorId="7" xr:uid="{89ccc38b-d7c7-4962-bad4-c5abec74ef0e}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Le cambiaron la transversalidad
-</t>
-      </text>
-    </comment>
-    <comment authorId="8" xr:uid="{a00864eb-706e-440e-8ebc-5902fb965ff6}" ref="I119">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Tiene recurso propio
+	Componente anterior (cambió de transversalidad)
 </t>
       </text>
     </comment>
@@ -116,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="444">
   <si>
     <t>UP</t>
   </si>
@@ -205,45 +225,45 @@
     <t>002</t>
   </si>
   <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>LOP</t>
+  </si>
+  <si>
+    <t>Programa por la Inclusión de Personas con Discapacidad</t>
+  </si>
+  <si>
     <t>SG1_CH</t>
   </si>
   <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>004</t>
-  </si>
-  <si>
-    <t>LOP</t>
-  </si>
-  <si>
-    <t>Programa por la Inclusión de Personas con Discapacidad</t>
+    <t>005</t>
+  </si>
+  <si>
+    <t>Apoyos a OSC para apoyo a la población de diversidad sexual</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>Atención y Oportunidades para las Juventudes No dejar a nadie atrás</t>
+  </si>
+  <si>
+    <t>007</t>
   </si>
   <si>
     <t>U</t>
   </si>
   <si>
-    <t>005</t>
+    <t>Programa Red de enlaces regionales del Mecanismo de Atención a Víctimas de Discriminación MAViD MAViDmun</t>
   </si>
   <si>
     <t>SG1_C1</t>
   </si>
   <si>
-    <t>Apoyos a OSC para apoyo a la población de diversidad sexual</t>
-  </si>
-  <si>
-    <t>006</t>
-  </si>
-  <si>
-    <t>Atención y Oportunidades para las Juventudes No dejar a nadie atrás</t>
-  </si>
-  <si>
-    <t>007</t>
-  </si>
-  <si>
-    <t>Programa Red de enlaces regionales del Mecanismo de Atención a Víctimas de Discriminación MAViD MAViDmun</t>
-  </si>
-  <si>
     <t>172</t>
   </si>
   <si>
@@ -256,33 +276,33 @@
     <t xml:space="preserve"> Apoyos económicos para los pueblos y comunidades indígenas</t>
   </si>
   <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>Becas por la Interculturalidad para estudiantes indígenas del nivel medio superior y superior</t>
+  </si>
+  <si>
+    <t>801</t>
+  </si>
+  <si>
+    <t>Comisión para la Búsqueda de Personas</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programa de Apoyo a Familiares de Personas Desaparecidas en el Estado de Jalisco </t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretaría de Hacienda </t>
+  </si>
+  <si>
     <t>SG1_C6</t>
   </si>
   <si>
-    <t>009</t>
-  </si>
-  <si>
-    <t>Becas por la Interculturalidad para estudiantes indígenas del nivel medio superior y superior</t>
-  </si>
-  <si>
-    <t>801</t>
-  </si>
-  <si>
-    <t>Comisión para la Búsqueda de Personas</t>
-  </si>
-  <si>
-    <t>010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programa de Apoyo a Familiares de Personas Desaparecidas en el Estado de Jalisco </t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Hacienda </t>
-  </si>
-  <si>
     <t>729</t>
   </si>
   <si>
@@ -292,30 +312,30 @@
     <t>011</t>
   </si>
   <si>
+    <t>Renovación parque vehicular transporte público</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>Reducción de la tarifa del transporte público para las personas usuarias</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretaría de Educación </t>
+  </si>
+  <si>
+    <t>097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programa Ayuda Económica para NIñas del Internado Beatriz Hernández </t>
+  </si>
+  <si>
     <t>SG1_CA</t>
   </si>
   <si>
-    <t>Renovación parque vehicular transporte público</t>
-  </si>
-  <si>
-    <t>012</t>
-  </si>
-  <si>
-    <t>Reducción de la tarifa del transporte público para las personas usuarias</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Educación </t>
-  </si>
-  <si>
-    <t>097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programa Ayuda Económica para NIñas del Internado Beatriz Hernández </t>
-  </si>
-  <si>
     <t>098</t>
   </si>
   <si>
@@ -325,21 +345,21 @@
     <t>099</t>
   </si>
   <si>
+    <t xml:space="preserve">Becas Talento </t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programa Ayuda Económica para las y los Estudiantes de la Escuela Normal Rural Miguel Hidalgo </t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
     <t>SG1_C5</t>
   </si>
   <si>
-    <t xml:space="preserve">Becas Talento </t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programa Ayuda Económica para las y los Estudiantes de la Escuela Normal Rural Miguel Hidalgo </t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
     <t>Secretaría de Desarrollo Económico</t>
   </si>
   <si>
@@ -349,759 +369,759 @@
     <t>Jalisco Atrae</t>
   </si>
   <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>Artesanías Jalisco Más</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>Impulso Mipymes Jalisco</t>
+  </si>
+  <si>
     <t>02_172</t>
   </si>
   <si>
-    <t>014</t>
+    <t>244</t>
+  </si>
+  <si>
+    <t>Fondo Impulso Jalisco</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>Impulso a la Competitividad, Talento y Vinculación al estilo Jalisco</t>
   </si>
   <si>
     <t>SJ7_C1</t>
   </si>
   <si>
-    <t>Artesanías Jalisco Más</t>
-  </si>
-  <si>
-    <t>015</t>
-  </si>
-  <si>
-    <t>Impulso Mipymes Jalisco</t>
-  </si>
-  <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>Fondo Impulso Jalisco</t>
-  </si>
-  <si>
-    <t>016</t>
-  </si>
-  <si>
-    <t>Impulso a la Competitividad, Talento y Vinculación al estilo Jalisco</t>
+    <t>017</t>
+  </si>
+  <si>
+    <t>Crecer al Estilo Jalisco mediante la generación de Empleo y Talento</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>Secretaría de Turismo</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>Programa para Desarrollo de productos y experiencias turísticas en el Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>Programa de apoyo a Producciones fílmicas y audiovisuales en el Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>Secretaría de Agricultura y Desarrollo Rural</t>
+  </si>
+  <si>
+    <t>020</t>
   </si>
   <si>
     <t>SJ7_C2</t>
   </si>
   <si>
-    <t>017</t>
-  </si>
-  <si>
-    <t>Crecer al Estilo Jalisco mediante la generación de Empleo y Talento</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>Secretaría de Turismo</t>
-  </si>
-  <si>
-    <t>018</t>
-  </si>
-  <si>
-    <t>Programa para Desarrollo de productos y experiencias turísticas en el Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>019</t>
-  </si>
-  <si>
-    <t>Programa de apoyo a Producciones fílmicas y audiovisuales en el Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>Secretaría de Agricultura y Desarrollo Rural</t>
-  </si>
-  <si>
-    <t>020</t>
-  </si>
-  <si>
     <t>Impulso Agro Jalisco. Producción y Tecnología</t>
   </si>
   <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>Jalisco Agrosustentable</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>Eficiencia verde cañera</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>Proyectos Estratégicos Agropecuarios, Pesqueros y Acuícolas al estilo Jalisco</t>
+  </si>
+  <si>
     <t>02_801</t>
   </si>
   <si>
+    <t>024</t>
+  </si>
+  <si>
+    <t>Proyectos Estratégicos Agroalimentarios.</t>
+  </si>
+  <si>
     <t>SBP_GA</t>
   </si>
   <si>
-    <t>021</t>
-  </si>
-  <si>
-    <t>Jalisco Agrosustentable</t>
-  </si>
-  <si>
-    <t>022</t>
-  </si>
-  <si>
-    <t>Eficiencia verde cañera</t>
+    <t>025</t>
+  </si>
+  <si>
+    <t>Empedrados al estilo Jalisco</t>
+  </si>
+  <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t>Fondo Jalisco para Contingencias Agroalimentarias</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>Apoyo a Cooperativas de la Laguna de Cajititlán</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>Fortalecimiento de Casas Ejidales</t>
   </si>
   <si>
     <t>03_729</t>
   </si>
   <si>
-    <t>023</t>
+    <t>029</t>
+  </si>
+  <si>
+    <t>Agroinnovadoras y Jóvenes del campo de Jalisco</t>
+  </si>
+  <si>
+    <t>190</t>
   </si>
   <si>
     <t>ST4_D1</t>
   </si>
   <si>
-    <t>Proyectos Estratégicos Agropecuarios, Pesqueros y Acuícolas al estilo Jalisco</t>
-  </si>
-  <si>
-    <t>024</t>
-  </si>
-  <si>
-    <t>Proyectos Estratégicos Agroalimentarios.</t>
-  </si>
-  <si>
-    <t>025</t>
-  </si>
-  <si>
-    <t>Empedrados al estilo Jalisco</t>
-  </si>
-  <si>
-    <t>026</t>
+    <t>Fideicomiso para Coberturas de Precios de Maíz</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>Fideicomiso para Coberturas de Precios de Maíz (LOP)</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>Agencia Estatal de Sanidad, Inocuidad y Calidad Agroalimentaria en Jalisco</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>Programa de Apoyo para el Fortalecimiento de la Inocuidad en Rastros en el Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>Programa de Eliminación de Animales Positivos, Reactores, Expuestos y Sospechosos</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>Programa de Apoyo para la Prevención y Control del Gusano Barrenador del Ganado en el Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretaría de Medio Ambiente y Desarrollo Territorial </t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O.P.D. Bosque la Primavera </t>
   </si>
   <si>
     <t>ST4_D2</t>
   </si>
   <si>
-    <t>Fondo Jalisco para Contingencias Agroalimentarias</t>
-  </si>
-  <si>
-    <t>027</t>
-  </si>
-  <si>
-    <t>Apoyo a Cooperativas de la Laguna de Cajititlán</t>
-  </si>
-  <si>
-    <t>028</t>
-  </si>
-  <si>
-    <t>Fortalecimiento de Casas Ejidales</t>
+    <t>034</t>
+  </si>
+  <si>
+    <t>Administración y Manejo del Área de Protección de Flora y Fauna La Primavera</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>Fideicomiso para la Administración del Programa de Desarrollo Forestal del Estado de Jalisco (FIPRODEFO)</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>Programa para el Desarrollo Forestal Sustentable del Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Secretaría del Sistema de Asistencia Social</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yo Jalisco Apoyo para la Salud Mental </t>
+  </si>
+  <si>
+    <t>037</t>
   </si>
   <si>
     <t>07_000</t>
   </si>
   <si>
-    <t>029</t>
+    <t>Yo Jalisco, Apoyo al Transporte</t>
   </si>
   <si>
     <t>S70_D1</t>
   </si>
   <si>
-    <t>Agroinnovadoras y Jóvenes del campo de Jalisco</t>
-  </si>
-  <si>
-    <t>190</t>
-  </si>
-  <si>
-    <t>Fideicomiso para Coberturas de Precios de Maíz</t>
-  </si>
-  <si>
-    <t>030</t>
-  </si>
-  <si>
-    <t>Fideicomiso para Coberturas de Precios de Maíz (LOP)</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>Agencia Estatal de Sanidad, Inocuidad y Calidad Agroalimentaria en Jalisco</t>
-  </si>
-  <si>
-    <t>031</t>
-  </si>
-  <si>
-    <t>Programa de Apoyo para el Fortalecimiento de la Inocuidad en Rastros en el Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>032</t>
+    <t>038</t>
+  </si>
+  <si>
+    <t>Yo Jalisco Apoyo a Personas Cuidadoras y Personas Dependientes de Cuidados</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>Yo Jalisco Apoyo para el Cuidado Infantil</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>Yo Jalisco, Apoyo a Instituciones de Cuidado Infantil</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yo Jalisco Apoyo a Jefas de Jalisco </t>
   </si>
   <si>
     <t>S71_C1</t>
   </si>
   <si>
-    <t>Programa de Eliminación de Animales Positivos, Reactores, Expuestos y Sospechosos</t>
-  </si>
-  <si>
-    <t>033</t>
-  </si>
-  <si>
-    <t>Programa de Apoyo para la Prevención y Control del Gusano Barrenador del Ganado en el Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Medio Ambiente y Desarrollo Territorial </t>
-  </si>
-  <si>
-    <t>042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O.P.D. Bosque la Primavera </t>
-  </si>
-  <si>
-    <t>034</t>
-  </si>
-  <si>
-    <t>Administración y Manejo del Área de Protección de Flora y Fauna La Primavera</t>
-  </si>
-  <si>
-    <t>043</t>
+    <t xml:space="preserve">Listo Jalisco </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yo Jalisco Apoyo a Asociaciones Civiles </t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>Yo Jalisco, Apoyo a Nuestras Comunidades</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>Yo Jalisco, Apoyo al Desarrollo Social</t>
   </si>
   <si>
     <t>S72_B1</t>
   </si>
   <si>
-    <t>Fideicomiso para la Administración del Programa de Desarrollo Forestal del Estado de Jalisco (FIPRODEFO)</t>
-  </si>
-  <si>
-    <t>035</t>
-  </si>
-  <si>
-    <t>Programa para el Desarrollo Forestal Sustentable del Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Secretaría del Sistema de Asistencia Social</t>
-  </si>
-  <si>
-    <t>036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yo Jalisco Apoyo para la Salud Mental </t>
-  </si>
-  <si>
-    <t>037</t>
-  </si>
-  <si>
-    <t>Yo Jalisco, Apoyo al Transporte</t>
+    <t>046</t>
+  </si>
+  <si>
+    <t>Enchulemos Jalisco</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>Yo Jalisco Transporte a Grupos Prioritarios</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>Yo Jalisco, Apoyo para nuestra gente</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Secretaría de Innovación, Ciencia y Tecnológia</t>
   </si>
   <si>
     <t>07_244</t>
   </si>
   <si>
-    <t>038</t>
+    <t>049</t>
+  </si>
+  <si>
+    <t>Fortalecimiento de ecosistemas regionales a través de la innovación y emprendimiento</t>
   </si>
   <si>
     <t>S7F_C1</t>
   </si>
   <si>
-    <t>Yo Jalisco Apoyo a Personas Cuidadoras y Personas Dependientes de Cuidados</t>
-  </si>
-  <si>
-    <t>039</t>
-  </si>
-  <si>
-    <t>Yo Jalisco Apoyo para el Cuidado Infantil</t>
-  </si>
-  <si>
-    <t>040</t>
-  </si>
-  <si>
-    <t>Yo Jalisco, Apoyo a Instituciones de Cuidado Infantil</t>
-  </si>
-  <si>
-    <t>041</t>
+    <t>050</t>
+  </si>
+  <si>
+    <t>Fortalecimiento de la Cultura de Innovación, Ciencia y Tecnología</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>Apoyos de Educación Superior para Jóvenes LEGADO</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>Impulso y Fortalecimiento a la Educación Superior</t>
+  </si>
+  <si>
+    <t>067</t>
   </si>
   <si>
     <t>S7F_C2</t>
   </si>
   <si>
-    <t xml:space="preserve">Yo Jalisco Apoyo a Jefas de Jalisco </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Listo Jalisco </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yo Jalisco Apoyo a Asociaciones Civiles </t>
+    <t>Consejo Estatal de Ciencia y Tecnología del Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>Gestión de fondos y programas de apoyo a la Ciencia, Tecnología e Innovación</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Agencia para el Desarrollo de Industrias Creativas y Digitales del Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>Fondo para Proyectos de Alto Impacto a la Industria Creativa Digital</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>Fondo Jalisco Creativo</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura</t>
   </si>
   <si>
     <t>08_000</t>
   </si>
   <si>
-    <t>044</t>
+    <t>Secretaría de cultura</t>
+  </si>
+  <si>
+    <t>056</t>
+  </si>
+  <si>
+    <t>Fondo Talleres en Casas de la Cultura</t>
   </si>
   <si>
     <t>S81_03</t>
   </si>
   <si>
-    <t>Yo Jalisco, Apoyo a Nuestras Comunidades</t>
-  </si>
-  <si>
-    <t>045</t>
-  </si>
-  <si>
-    <t>Yo Jalisco, Apoyo al Desarrollo Social</t>
-  </si>
-  <si>
-    <t>046</t>
-  </si>
-  <si>
-    <t>Enchulemos Jalisco</t>
-  </si>
-  <si>
-    <t>047</t>
-  </si>
-  <si>
-    <t>Yo Jalisco Transporte a Grupos Prioritarios</t>
+    <t>057</t>
+  </si>
+  <si>
+    <t>Fondo Jalisco de Animación Cultural</t>
+  </si>
+  <si>
+    <t>058</t>
+  </si>
+  <si>
+    <t>Programa de Apoyo a las Cultura Municipales y Comunitarias (PACMYC)</t>
+  </si>
+  <si>
+    <t>059</t>
+  </si>
+  <si>
+    <t>Programa de Estímulo a la Creación y al Desarrollo Artístico (PECDA)</t>
   </si>
   <si>
     <t>S81_06</t>
   </si>
   <si>
-    <t>048</t>
-  </si>
-  <si>
-    <t>Yo Jalisco, Apoyo para nuestra gente</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Secretaría de Innovación, Ciencia y Tecnológia</t>
-  </si>
-  <si>
-    <t>049</t>
-  </si>
-  <si>
-    <t>Fortalecimiento de ecosistemas regionales a través de la innovación y emprendimiento</t>
+    <t>060</t>
+  </si>
+  <si>
+    <t>Proyecta Producción</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>Proyecta Traslados</t>
+  </si>
+  <si>
+    <t>062</t>
+  </si>
+  <si>
+    <t>Programa de Fomento Editorial</t>
+  </si>
+  <si>
+    <t>063</t>
   </si>
   <si>
     <t>09_000</t>
   </si>
   <si>
-    <t>050</t>
+    <t>Habita la Escena</t>
+  </si>
+  <si>
+    <t>083</t>
   </si>
   <si>
     <t>S91_D8</t>
   </si>
   <si>
-    <t>Fortalecimiento de la Cultura de Innovación, Ciencia y Tecnología</t>
-  </si>
-  <si>
-    <t>051</t>
-  </si>
-  <si>
-    <t>Apoyos de Educación Superior para Jóvenes LEGADO</t>
-  </si>
-  <si>
-    <t>052</t>
-  </si>
-  <si>
-    <t>Impulso y Fortalecimiento a la Educación Superior</t>
-  </si>
-  <si>
-    <t>067</t>
-  </si>
-  <si>
-    <t>Consejo Estatal de Ciencia y Tecnología del Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>053</t>
+    <t>Fideicomiso Fondo Estatal para la Cultura y las Artes FEFCA</t>
+  </si>
+  <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>Programa ECOS, Música para la Paz</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Secretaría de Trabajo y Previsión Social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretaría de Trabajo y Previsión Social </t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empleo Temporal al Estilo Jalisco  </t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jale seguro al estilo Jalisco </t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programa Apoyo al Empleo </t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>S92_D1</t>
   </si>
   <si>
-    <t>Gestión de fondos y programas de apoyo a la Ciencia, Tecnología e Innovación</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>Agencia para el Desarrollo de Industrias Creativas y Digitales del Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>054</t>
-  </si>
-  <si>
-    <t>Fondo para Proyectos de Alto Impacto a la Industria Creativa Digital</t>
-  </si>
-  <si>
-    <t>055</t>
-  </si>
-  <si>
-    <t>Fondo Jalisco Creativo</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura</t>
-  </si>
-  <si>
-    <t>Secretaría de cultura</t>
+    <t xml:space="preserve">Secretaría de Transporte </t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>Mujeres Conductoras Al Estilo Jalisco (LOP)</t>
+  </si>
+  <si>
+    <t>066</t>
+  </si>
+  <si>
+    <t>Mujeres Conductoras Al Estilo Jalisco (ROP)</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretaría de Gestión Integral del Agua </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comisión Estatal del Agua </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nidos de LLuvia </t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretaría de Igualdad Sustantiva entre Mujeres y Hombres </t>
+  </si>
+  <si>
+    <t>068</t>
   </si>
   <si>
     <t>S92_D2</t>
   </si>
   <si>
-    <t>056</t>
-  </si>
-  <si>
-    <t>Fondo Talleres en Casas de la Cultura</t>
-  </si>
-  <si>
-    <t>057</t>
-  </si>
-  <si>
-    <t>Fondo Jalisco de Animación Cultural</t>
-  </si>
-  <si>
-    <t>058</t>
-  </si>
-  <si>
-    <t>Programa de Apoyo a las Cultura Municipales y Comunitarias (PACMYC)</t>
+    <t xml:space="preserve">Fuerza Mujeres </t>
+  </si>
+  <si>
+    <t>069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empresarias de Alto Impacto </t>
+  </si>
+  <si>
+    <t>070</t>
+  </si>
+  <si>
+    <t>Apoyos económicos para las Hijas e Hijos de Mujeres Víctimas de Feminicidio</t>
+  </si>
+  <si>
+    <t>071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrios de Paz </t>
   </si>
   <si>
     <t>S95_D1</t>
   </si>
   <si>
-    <t>059</t>
-  </si>
-  <si>
-    <t>Programa de Estímulo a la Creación y al Desarrollo Artístico (PECDA)</t>
-  </si>
-  <si>
-    <t>060</t>
-  </si>
-  <si>
-    <t>Proyecta Producción</t>
-  </si>
-  <si>
-    <t>061</t>
-  </si>
-  <si>
-    <t>Proyecta Traslados</t>
-  </si>
-  <si>
-    <t>062</t>
-  </si>
-  <si>
-    <t>Programa de Fomento Editorial</t>
+    <t>072</t>
+  </si>
+  <si>
+    <t>Estrategia Ale</t>
+  </si>
+  <si>
+    <t>073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asosiaciones por la Igualdad </t>
+  </si>
+  <si>
+    <t>096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red de Centros de Justicia para las Mujeres </t>
+  </si>
+  <si>
+    <t>074</t>
+  </si>
+  <si>
+    <t>Reglas de Operación para la Atención Especializada de Necesidades Complementarias de las Usuarias de los Centros de Justicia para las Mujeres del Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Coordinación General Estratégica de Desarrollo Social</t>
+  </si>
+  <si>
+    <t>Sistema para el Desarrollo Integral de la Familia Jalisco (DIF)</t>
+  </si>
+  <si>
+    <t>075</t>
+  </si>
+  <si>
+    <t>Programa de Atención a Grupos Prioritarios</t>
   </si>
   <si>
     <t>S95_D3</t>
   </si>
   <si>
-    <t>063</t>
-  </si>
-  <si>
-    <t>Habita la Escena</t>
-  </si>
-  <si>
-    <t>083</t>
-  </si>
-  <si>
-    <t>Fideicomiso Fondo Estatal para la Cultura y las Artes FEFCA</t>
-  </si>
-  <si>
-    <t>064</t>
-  </si>
-  <si>
-    <t>Programa ECOS, Música para la Paz</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Secretaría de Trabajo y Previsión Social</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Trabajo y Previsión Social </t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empleo Temporal al Estilo Jalisco  </t>
-  </si>
-  <si>
-    <t>102</t>
+    <t>076</t>
+  </si>
+  <si>
+    <t>Programa de Salud y Bienestar Comunitario PSBC</t>
+  </si>
+  <si>
+    <t>077</t>
+  </si>
+  <si>
+    <t>Programa DIF Pilares</t>
   </si>
   <si>
     <t>S96_D4</t>
   </si>
   <si>
-    <t xml:space="preserve">Jale seguro al estilo Jalisco </t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programa Apoyo al Empleo </t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Transporte </t>
-  </si>
-  <si>
-    <t>065</t>
-  </si>
-  <si>
-    <t>Mujeres Conductoras Al Estilo Jalisco (LOP)</t>
-  </si>
-  <si>
-    <t>066</t>
+    <t>078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apoyos Asistenciales a Personas en Situación Prioritaria </t>
+  </si>
+  <si>
+    <t>079</t>
+  </si>
+  <si>
+    <t>Estrategias de formación y apoyos económicos otorgados para la prevención de riesgos psicosociales y atención a la niñez</t>
+  </si>
+  <si>
+    <t>080</t>
+  </si>
+  <si>
+    <t>Acompañar la ausencia a personas familiares víctimas indirectas de una desaparición, en el Estado de Jalisco: apoyo a municipios (nombre preeliminar)</t>
+  </si>
+  <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>Apoyos asistenciales otorgados a población vulnerable. (Nombre preeliminar)</t>
   </si>
   <si>
     <t>S98_D1</t>
   </si>
   <si>
-    <t>Mujeres Conductoras Al Estilo Jalisco (ROP)</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Gestión Integral del Agua </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comisión Estatal del Agua </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nidos de LLuvia </t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secretaría de Igualdad Sustantiva entre Mujeres y Hombres </t>
-  </si>
-  <si>
-    <t>068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuerza Mujeres </t>
+    <t>082</t>
+  </si>
+  <si>
+    <t>Acompañar la ausencia a personas familiares víctimas indirectas de una desaparición, en el Estado de Jalisco: apoyo directo (Nombre preeliminar)</t>
+  </si>
+  <si>
+    <t>Atención y Representación de Niñas, Niños y Adolescentes para la Protección y Restitución de sus Derechos en el Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>084</t>
+  </si>
+  <si>
+    <t>Fortalecer las acciones para la atención y/o reintegración de personas en situación de calle, en contexto de movilidad, tránsito, retorno o en condición de vulnerabilidad en el estado de Jalisco</t>
   </si>
   <si>
     <t>S98_D2</t>
   </si>
   <si>
-    <t>069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empresarias de Alto Impacto </t>
-  </si>
-  <si>
-    <t>070</t>
-  </si>
-  <si>
-    <t>Apoyos económicos para las Hijas e Hijos de Mujeres Víctimas de Feminicidio</t>
-  </si>
-  <si>
-    <t>071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrios de Paz </t>
+    <t>085</t>
+  </si>
+  <si>
+    <t>Apoyos a Personas con Discapacidad en el Estado de Jalisco</t>
+  </si>
+  <si>
+    <t>086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias Económicas para el Fortalecimiento de la Atención Alimentaria </t>
+  </si>
+  <si>
+    <t>087</t>
+  </si>
+  <si>
+    <t>Equipamientos para Fortalecer la Atención Alimentaria</t>
+  </si>
+  <si>
+    <t>088</t>
+  </si>
+  <si>
+    <t>Programa de Alimentación Escolar</t>
   </si>
   <si>
     <t>S99_D1</t>
   </si>
   <si>
-    <t>072</t>
-  </si>
-  <si>
-    <t>Estrategia Ale</t>
-  </si>
-  <si>
-    <t>073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asosiaciones por la Igualdad </t>
-  </si>
-  <si>
-    <t>096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red de Centros de Justicia para las Mujeres </t>
-  </si>
-  <si>
-    <t>074</t>
-  </si>
-  <si>
-    <t>Reglas de Operación para la Atención Especializada de Necesidades Complementarias de las Usuarias de los Centros de Justicia para las Mujeres del Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>Coordinación General Estratégica de Desarrollo Social</t>
-  </si>
-  <si>
-    <t>Sistema para el Desarrollo Integral de la Familia Jalisco (DIF)</t>
-  </si>
-  <si>
-    <t>075</t>
-  </si>
-  <si>
-    <t>Programa de Atención a Grupos Prioritarios</t>
-  </si>
-  <si>
-    <t>076</t>
-  </si>
-  <si>
-    <t>Programa de Salud y Bienestar Comunitario PSBC</t>
+    <t>089</t>
+  </si>
+  <si>
+    <t>Programa de Atención Alimentaria a Personas en Situación de Vulnerabilidad</t>
+  </si>
+  <si>
+    <t>090</t>
+  </si>
+  <si>
+    <t>Programa de Atención Alimentaria en los Primeros 1,000 Días y Primera Infancia</t>
+  </si>
+  <si>
+    <t>091</t>
+  </si>
+  <si>
+    <t>Comedores Comunitarios</t>
+  </si>
+  <si>
+    <t>092</t>
+  </si>
+  <si>
+    <t>Despensas Alimentarias</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Instituto Jalisciense de la Vivienda</t>
+  </si>
+  <si>
+    <t>093</t>
+  </si>
+  <si>
+    <t>Mi Primera Renta</t>
+  </si>
+  <si>
+    <t>094</t>
+  </si>
+  <si>
+    <t>Acondicionamiento de Vivienda para PCD (Recurso propio)</t>
   </si>
   <si>
     <t>S99_D2</t>
   </si>
   <si>
-    <t>077</t>
-  </si>
-  <si>
-    <t>Programa DIF Pilares</t>
-  </si>
-  <si>
-    <t>078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apoyos Asistenciales a Personas en Situación Prioritaria </t>
-  </si>
-  <si>
-    <t>079</t>
+    <t>095</t>
+  </si>
+  <si>
+    <t>Mejoramiento de Vivienda</t>
+  </si>
+  <si>
+    <t>Jalisco Si Pinta (Recurso propio)</t>
   </si>
   <si>
     <t>S99_B3</t>
   </si>
   <si>
-    <t>Estrategias de formación y apoyos económicos otorgados para la prevención de riesgos psicosociales y atención a la niñez</t>
-  </si>
-  <si>
-    <t>080</t>
-  </si>
-  <si>
-    <t>Acompañar la ausencia a personas familiares víctimas indirectas de una desaparición, en el Estado de Jalisco: apoyo a municipios (nombre preeliminar)</t>
-  </si>
-  <si>
-    <t>081</t>
-  </si>
-  <si>
-    <t>Apoyos asistenciales otorgados a población vulnerable. (Nombre preeliminar)</t>
-  </si>
-  <si>
     <t>09_190</t>
   </si>
   <si>
-    <t>082</t>
-  </si>
-  <si>
     <t>S9C_D1</t>
   </si>
   <si>
-    <t>Acompañar la ausencia a personas familiares víctimas indirectas de una desaparición, en el Estado de Jalisco: apoyo directo (Nombre preeliminar)</t>
-  </si>
-  <si>
-    <t>Atención y Representación de Niñas, Niños y Adolescentes para la Protección y Restitución de sus Derechos en el Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>084</t>
-  </si>
-  <si>
-    <t>Fortalecer las acciones para la atención y/o reintegración de personas en situación de calle, en contexto de movilidad, tránsito, retorno o en condición de vulnerabilidad en el estado de Jalisco</t>
-  </si>
-  <si>
     <t>09_225</t>
   </si>
   <si>
-    <t>085</t>
-  </si>
-  <si>
     <t>S9E_C1</t>
   </si>
   <si>
-    <t>Apoyos a Personas con Discapacidad en el Estado de Jalisco</t>
-  </si>
-  <si>
-    <t>086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transferencias Económicas para el Fortalecimiento de la Atención Alimentaria </t>
-  </si>
-  <si>
-    <t>087</t>
-  </si>
-  <si>
-    <t>Equipamientos para Fortalecer la Atención Alimentaria</t>
-  </si>
-  <si>
-    <t>088</t>
-  </si>
-  <si>
     <t>S9E_C2</t>
   </si>
   <si>
-    <t>Programa de Alimentación Escolar</t>
-  </si>
-  <si>
-    <t>089</t>
-  </si>
-  <si>
-    <t>Programa de Atención Alimentaria a Personas en Situación de Vulnerabilidad</t>
-  </si>
-  <si>
-    <t>090</t>
-  </si>
-  <si>
-    <t>Programa de Atención Alimentaria en los Primeros 1,000 Días y Primera Infancia</t>
-  </si>
-  <si>
-    <t>091</t>
-  </si>
-  <si>
-    <t>Comedores Comunitarios</t>
-  </si>
-  <si>
     <t>S9E_D3</t>
   </si>
   <si>
-    <t>092</t>
-  </si>
-  <si>
-    <t>Despensas Alimentarias</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>Instituto Jalisciense de la Vivienda</t>
-  </si>
-  <si>
-    <t>093</t>
-  </si>
-  <si>
-    <t>Mi Primera Renta</t>
-  </si>
-  <si>
-    <t>094</t>
-  </si>
-  <si>
     <t>10_042</t>
   </si>
   <si>
-    <t>Acondicionamiento de Vivienda para PCD (Recurso propio)</t>
-  </si>
-  <si>
     <t>S1C_D1</t>
   </si>
   <si>
-    <t>095</t>
-  </si>
-  <si>
-    <t>Mejoramiento de Vivienda</t>
-  </si>
-  <si>
-    <t>Jalisco Si Pinta (Recurso propio)</t>
-  </si>
-  <si>
     <t>S1C_D2</t>
   </si>
   <si>
@@ -1132,6 +1152,9 @@
     <t>S03_B8</t>
   </si>
   <si>
+    <t>S03_C4</t>
+  </si>
+  <si>
     <t>S03_C5</t>
   </si>
   <si>
@@ -1406,6 +1429,9 @@
   </si>
   <si>
     <t>SE6_A4</t>
+  </si>
+  <si>
+    <t>SE6_B4</t>
   </si>
   <si>
     <t>14_000</t>
@@ -1576,17 +1602,17 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{7b364871-8331-40bd-b527-02d9253d1f17}" providerId="google-sheets"/>
-  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{d0018b8d-5a82-4fc6-ab0a-4b7cb68e33ef}" providerId="google-sheets"/>
-  <x18tc:person displayName="Armando Yair Cárdenas Ávila" id="{114bd514-c3fa-4588-8947-87706c00e071}" providerId="google-sheets"/>
-  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{3dd7d5bc-298c-4e30-97c3-2caede612f88}" providerId="google-sheets"/>
+  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{d588f755-4778-4ac3-b440-b15faef6ceff}" providerId="google-sheets"/>
+  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{e9e1fb8d-f948-4cb8-ad63-6b2a86cd3555}" providerId="google-sheets"/>
+  <x18tc:person displayName="Armando Yair Cárdenas Ávila" id="{dac9c582-67e0-47da-840e-3f79f582095d}" providerId="google-sheets"/>
+  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{25f5eabf-fe88-4321-bee4-09fb72b64639}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" invalid="1" refreshOnLoad="1">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:AA1062" sheet="Hoja 1"/>
+    <worksheetSource ref="A1:AA1064" sheet="Hoja 1"/>
   </cacheSource>
   <cacheFields>
     <cacheField name="UP" numFmtId="49">
@@ -1775,6 +1801,7 @@
         <s v="S03_C2"/>
         <s v="S03_C3"/>
         <s v="S03_B8"/>
+        <s v="S03_C4"/>
         <s v="S03_C5"/>
         <s v="S03_C6"/>
         <s v="S03_A7"/>
@@ -1853,6 +1880,7 @@
         <s v="SE3_A1"/>
         <s v="SE3_A2"/>
         <s v="SE6_A4"/>
+        <s v="SE6_B4"/>
         <s v="S41_C1"/>
         <s v="S41_C2"/>
         <s v="S48_01"/>
@@ -2456,6 +2484,8 @@
         <item x="131"/>
         <item x="132"/>
         <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2993,32 +3023,38 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="F85" dT="2026-06-25T21:11:19.00" personId="{3dd7d5bc-298c-4e30-97c3-2caede612f88}" id="{22233615-6a31-45f6-85e9-d87008445735}" done="1">
+  <x18tc:threadedComment ref="F86" dT="2026-06-25T21:11:19.00" personId="{25f5eabf-fe88-4321-bee4-09fb72b64639}" id="{cc49baf0-5f50-4e72-880a-13eb15cdcc18}" done="1">
     <x18tc:text xml:space="preserve">Actalmente es un Lineamiento de Operación</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F16" dT="2026-06-25T21:15:11.00" personId="{3dd7d5bc-298c-4e30-97c3-2caede612f88}" id="{3cf0f526-fed6-4970-8110-6c1a561ba207}" done="1">
+  <x18tc:threadedComment ref="F16" dT="2026-06-25T21:15:11.00" personId="{25f5eabf-fe88-4321-bee4-09fb72b64639}" id="{5298d5ab-eb5a-40c5-a769-325a49962664}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con clasificación Programpatica  E</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F16" dT="2026-06-25T21:43:13.00" personId="{3dd7d5bc-298c-4e30-97c3-2caede612f88}" id="{084650f0-ece0-464c-b53c-a4306a96e34a}" done="1">
+  <x18tc:threadedComment ref="F16" dT="2026-06-25T21:43:13.00" personId="{25f5eabf-fe88-4321-bee4-09fb72b64639}" id="{a94b4d88-de05-4cad-88dc-c7ff14a36a20}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con una clasificación programática con letra E</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="I37" dT="2026-07-06T19:48:27.00" personId="{7b364871-8331-40bd-b527-02d9253d1f17}" id="{8100cc0a-5966-42ae-82f9-381e2e5b42a8}" done="1">
+  <x18tc:threadedComment ref="I37" dT="2026-07-06T19:48:27.00" personId="{d588f755-4778-4ac3-b440-b15faef6ceff}" id="{7bd4eed0-cf44-4594-bfa5-0a45225cbe5d}" done="1">
     <x18tc:text xml:space="preserve">A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{7b364871-8331-40bd-b527-02d9253d1f17}" id="{441d2b04-d373-4a9c-af6a-4de0d1fdb33e}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{d588f755-4778-4ac3-b440-b15faef6ceff}" id="{57366feb-1f43-4800-9540-a1243fb02836}" done="0">
     <x18tc:text xml:space="preserve">De momento se registra el nombre del componente; a la espera de nombre de la ROP.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-03T23:05:51.00" personId="{d0018b8d-5a82-4fc6-ab0a-4b7cb68e33ef}" id="{89ccc38b-d7c7-4962-bad4-c5abec74ef0e}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-03T23:05:51.00" personId="{e9e1fb8d-f948-4cb8-ad63-6b2a86cd3555}" id="{9a62354d-f2a3-4594-b6b3-01b8d11f20f1}" done="0">
     <x18tc:text xml:space="preserve">Le cambiaron la transversalidad</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="I121" dT="2026-08-12T23:13:36.00" personId="{114bd514-c3fa-4588-8947-87706c00e071}" id="{69da3166-d45c-4dff-ac98-f25200ba1c98}" done="1">
+  <x18tc:threadedComment ref="I122" dT="2026-08-12T23:13:36.00" personId="{dac9c582-67e0-47da-840e-3f79f582095d}" id="{df2ba1e2-2b7d-45cd-9d5b-74290b0746d2}" done="1">
     <x18tc:text xml:space="preserve">Solo tiene recurso propio</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="I119" dT="2026-08-12T23:13:08.00" personId="{114bd514-c3fa-4588-8947-87706c00e071}" id="{a00864eb-706e-440e-8ebc-5902fb965ff6}" done="1">
+  <x18tc:threadedComment ref="I120" dT="2026-08-12T23:13:08.00" personId="{dac9c582-67e0-47da-840e-3f79f582095d}" id="{b31cd7ed-42a8-45af-acfe-c2ec20c8a2b6}" done="1">
     <x18tc:text xml:space="preserve">Tiene recurso propio</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="H33" dT="2026-09-15T18:45:08.00" personId="{7b364871-8331-40bd-b527-02d9253d1f17}" id="{4e3e344e-aaf2-4972-b3a3-c64713db101d}" done="0">
+  <x18tc:threadedComment ref="H33" dT="2026-09-15T18:45:08.00" personId="{d588f755-4778-4ac3-b440-b15faef6ceff}" id="{b47461d1-de0e-47d4-b614-4d8bb7e9ec82}" done="0">
     <x18tc:text xml:space="preserve">Se eliminó componente.</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="H127" dT="2026-10-14T15:35:01.00" personId="{dac9c582-67e0-47da-840e-3f79f582095d}" id="{ff932e4d-2f32-4ebb-bd88-696a66e50400}" done="0">
+    <x18tc:text xml:space="preserve">Componente anterior (cambió de transversalidad)</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="H48" dT="2026-10-14T15:35:57.00" personId="{dac9c582-67e0-47da-840e-3f79f582095d}" id="{a204895e-58cf-4d20-af7f-93bb9067096f}" done="0">
+    <x18tc:text xml:space="preserve">Componente anterior (cambió de transversalidad)</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
 </file>
@@ -3147,7 +3183,7 @@
         <v>16</v>
       </c>
       <c r="G2" s="5" t="str">
-        <f t="shared" ref="G2:G134" si="1">IF(F2="S","ROP","LOP")</f>
+        <f t="shared" ref="G2:G136" si="1">IF(F2="S","ROP","LOP")</f>
         <v>ROP</v>
       </c>
       <c r="H2" s="5" t="s">
@@ -3160,7 +3196,7 @@
         <v>19</v>
       </c>
       <c r="K2" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I2,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I2,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="L2" s="5"/>
@@ -3213,7 +3249,7 @@
         <v>19</v>
       </c>
       <c r="K3" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I3,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I3,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="L3" s="4"/>
@@ -3266,7 +3302,7 @@
         <v>19</v>
       </c>
       <c r="K4" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I4,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I4,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="L4" s="4"/>
@@ -3319,7 +3355,7 @@
         <v>19</v>
       </c>
       <c r="K5" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I5,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"002")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I5,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"002")</f>
         <v>002</v>
       </c>
       <c r="L5" s="4"/>
@@ -3372,7 +3408,7 @@
         <v>19</v>
       </c>
       <c r="K6" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I6,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"003")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I6,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"003")</f>
         <v>003</v>
       </c>
       <c r="L6" s="4"/>
@@ -3416,7 +3452,7 @@
         <v>ROP</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>18</v>
@@ -3425,7 +3461,7 @@
         <v>19</v>
       </c>
       <c r="K7" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I7,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I7,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="L7" s="4"/>
@@ -3462,23 +3498,23 @@
         <v>13</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G8" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K8" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I8,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"004")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I8,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"004")</f>
         <v>004</v>
       </c>
       <c r="L8" s="4"/>
@@ -3515,23 +3551,23 @@
         <v>13</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G9" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K9" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I9,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"005")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I9,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"005")</f>
         <v>005</v>
       </c>
       <c r="L9" s="4"/>
@@ -3568,23 +3604,23 @@
         <v>13</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G10" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K10" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I10,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"006")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I10,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"006")</f>
         <v>006</v>
       </c>
       <c r="L10" s="4"/>
@@ -3621,23 +3657,23 @@
         <v>13</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G11" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I11,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"007")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I11,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"007")</f>
         <v>007</v>
       </c>
       <c r="L11" s="4"/>
@@ -3668,7 +3704,7 @@
         <v>42</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>43</v>
@@ -3681,7 +3717,7 @@
         <v>ROP</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>45</v>
@@ -3690,7 +3726,7 @@
         <v>19</v>
       </c>
       <c r="K12" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I12,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"008")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I12,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"008")</f>
         <v>008</v>
       </c>
       <c r="L12" s="4"/>
@@ -3721,7 +3757,7 @@
         <v>42</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>43</v>
@@ -3734,16 +3770,16 @@
         <v>ROP</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K13" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I13,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"009")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I13,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"009")</f>
         <v>009</v>
       </c>
       <c r="L13" s="4"/>
@@ -3771,13 +3807,13 @@
         <v>13</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>16</v>
@@ -3787,16 +3823,16 @@
         <v>ROP</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K14" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I14,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"010")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I14,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"010")</f>
         <v>010</v>
       </c>
       <c r="L14" s="4"/>
@@ -3818,16 +3854,16 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>55</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>56</v>
@@ -3840,16 +3876,16 @@
         <v>ROP</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I15,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"011")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I15,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"011")</f>
         <v>011</v>
       </c>
       <c r="L15" s="4"/>
@@ -3871,38 +3907,38 @@
     </row>
     <row r="16">
       <c r="A16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>55</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>56</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G16" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I16,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"012")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I16,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"012")</f>
         <v>012</v>
       </c>
       <c r="L16" s="4"/>
@@ -3924,7 +3960,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>74</v>
@@ -3933,7 +3969,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>74</v>
@@ -3946,7 +3982,7 @@
         <v>ROP</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>76</v>
@@ -3955,7 +3991,7 @@
         <v>19</v>
       </c>
       <c r="K17" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I17,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"013")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I17,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"013")</f>
         <v>013</v>
       </c>
       <c r="L17" s="4"/>
@@ -3977,7 +4013,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>74</v>
@@ -3986,7 +4022,7 @@
         <v>14</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>74</v>
@@ -3999,16 +4035,16 @@
         <v>ROP</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K18" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I18,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"014")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I18,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"014")</f>
         <v>014</v>
       </c>
       <c r="L18" s="4"/>
@@ -4030,7 +4066,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>74</v>
@@ -4039,7 +4075,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>74</v>
@@ -4052,16 +4088,16 @@
         <v>ROP</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K19" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I19,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"015")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I19,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"015")</f>
         <v>015</v>
       </c>
       <c r="L19" s="4"/>
@@ -4083,38 +4119,38 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>74</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="F20" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G20" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K20" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I20,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"016")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I20,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"016")</f>
         <v>016</v>
       </c>
       <c r="L20" s="4"/>
@@ -4136,19 +4172,19 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>74</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>16</v>
@@ -4158,16 +4194,16 @@
         <v>ROP</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K21" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I21,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"017")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I21,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"017")</f>
         <v>017</v>
       </c>
       <c r="L21" s="4"/>
@@ -4189,38 +4225,38 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G22" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K22" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I22,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"018")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I22,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"018")</f>
         <v>018</v>
       </c>
       <c r="L22" s="4"/>
@@ -4242,19 +4278,19 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>16</v>
@@ -4264,16 +4300,16 @@
         <v>ROP</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K23" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I23,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"019")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I23,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"019")</f>
         <v>019</v>
       </c>
       <c r="L23" s="4"/>
@@ -4295,19 +4331,19 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>16</v>
@@ -4317,7 +4353,7 @@
         <v>ROP</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>99</v>
@@ -4326,7 +4362,7 @@
         <v>19</v>
       </c>
       <c r="K24" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I24,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"020")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I24,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"020")</f>
         <v>020</v>
       </c>
       <c r="L24" s="4"/>
@@ -4348,19 +4384,19 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>16</v>
@@ -4370,16 +4406,16 @@
         <v>ROP</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>196</v>
+        <v>236</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K25" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I25,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"021")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I25,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"021")</f>
         <v>021</v>
       </c>
       <c r="L25" s="4"/>
@@ -4401,19 +4437,19 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>16</v>
@@ -4423,16 +4459,16 @@
         <v>ROP</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>207</v>
+        <v>249</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K26" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I26,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"022")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I26,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"022")</f>
         <v>022</v>
       </c>
       <c r="L26" s="4"/>
@@ -4454,19 +4490,19 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>16</v>
@@ -4476,16 +4512,16 @@
         <v>ROP</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>214</v>
+        <v>257</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K27" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I27,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"023")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I27,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"023")</f>
         <v>023</v>
       </c>
       <c r="L27" s="4"/>
@@ -4507,38 +4543,38 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G28" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>223</v>
+        <v>271</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K28" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I28,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"024")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I28,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"024")</f>
         <v>024</v>
       </c>
       <c r="L28" s="4"/>
@@ -4560,38 +4596,38 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G29" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>236</v>
+        <v>276</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K29" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I29,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"025")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I29,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"025")</f>
         <v>025</v>
       </c>
       <c r="L29" s="4"/>
@@ -4613,19 +4649,19 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>16</v>
@@ -4635,16 +4671,16 @@
         <v>ROP</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>245</v>
+        <v>285</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K30" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I30,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"026")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I30,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"026")</f>
         <v>026</v>
       </c>
       <c r="L30" s="4"/>
@@ -4666,19 +4702,19 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>16</v>
@@ -4688,16 +4724,16 @@
         <v>ROP</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K31" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I31,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"027")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I31,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"027")</f>
         <v>027</v>
       </c>
       <c r="L31" s="4"/>
@@ -4719,19 +4755,19 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>16</v>
@@ -4741,16 +4777,16 @@
         <v>ROP</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K32" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I32,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"028")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I32,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"028")</f>
         <v>028</v>
       </c>
       <c r="L32" s="4"/>
@@ -4772,19 +4808,19 @@
     </row>
     <row r="33">
       <c r="A33" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>16</v>
@@ -4794,16 +4830,16 @@
         <v>ROP</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K33" s="10" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I33,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"028")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I33,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"028")</f>
         <v>028</v>
       </c>
       <c r="L33" s="4"/>
@@ -4825,19 +4861,19 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>16</v>
@@ -4847,16 +4883,16 @@
         <v>ROP</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="J34" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K34" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I34,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"029")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I34,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"029")</f>
         <v>029</v>
       </c>
       <c r="L34" s="4"/>
@@ -4878,38 +4914,38 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="C35" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G35" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J35" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K35" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I35,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"030")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I35,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"030")</f>
         <v>030</v>
       </c>
       <c r="L35" s="4"/>
@@ -4931,38 +4967,38 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="C36" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G36" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J36" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K36" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I36,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"031")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I36,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"031")</f>
         <v>031</v>
       </c>
       <c r="L36" s="4"/>
@@ -4984,19 +5020,19 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="C37" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>16</v>
@@ -5006,16 +5042,16 @@
         <v>ROP</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="J37" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K37" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I37,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"032")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I37,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"032")</f>
         <v>032</v>
       </c>
       <c r="L37" s="5"/>
@@ -5037,38 +5073,38 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="C38" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G38" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J38" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K38" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I38,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"033")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I38,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"033")</f>
         <v>033</v>
       </c>
       <c r="L38" s="4"/>
@@ -5090,19 +5126,19 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>16</v>
@@ -5112,16 +5148,16 @@
         <v>ROP</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J39" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K39" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I39,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"034")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I39,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"034")</f>
         <v>034</v>
       </c>
       <c r="L39" s="4"/>
@@ -5143,19 +5179,19 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>16</v>
@@ -5168,13 +5204,13 @@
         <v>328</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K40" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I40,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"034")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I40,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"034")</f>
         <v>034</v>
       </c>
       <c r="L40" s="4"/>
@@ -5196,19 +5232,19 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>16</v>
@@ -5221,13 +5257,13 @@
         <v>329</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J41" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K41" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I41,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"034")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I41,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"034")</f>
         <v>034</v>
       </c>
       <c r="L41" s="4"/>
@@ -5249,19 +5285,19 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>330</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>16</v>
@@ -5274,13 +5310,13 @@
         <v>331</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="J42" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K42" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I42,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"035")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I42,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"035")</f>
         <v>035</v>
       </c>
       <c r="L42" s="4"/>
@@ -5302,10 +5338,10 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>14</v>
@@ -5314,10 +5350,10 @@
         <v>332</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G43" s="5" t="str">
         <f t="shared" si="1"/>
@@ -5327,13 +5363,13 @@
         <v>333</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="J43" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K43" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I43,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"036")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I43,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"036")</f>
         <v>036</v>
       </c>
       <c r="L43" s="4"/>
@@ -5355,10 +5391,10 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>14</v>
@@ -5367,7 +5403,7 @@
         <v>332</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>16</v>
@@ -5380,13 +5416,13 @@
         <v>334</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J44" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K44" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I44,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I44,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="L44" s="4"/>
@@ -5408,10 +5444,10 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>14</v>
@@ -5420,7 +5456,7 @@
         <v>332</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>16</v>
@@ -5433,13 +5469,13 @@
         <v>335</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J45" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K45" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I45,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I45,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="L45" s="4"/>
@@ -5461,10 +5497,10 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>14</v>
@@ -5473,7 +5509,7 @@
         <v>332</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>16</v>
@@ -5486,13 +5522,13 @@
         <v>336</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J46" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K46" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I46,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I46,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="L46" s="4"/>
@@ -5514,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>14</v>
@@ -5526,7 +5562,7 @@
         <v>332</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>16</v>
@@ -5539,13 +5575,13 @@
         <v>337</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J47" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K47" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I47,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I47,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="L47" s="4"/>
@@ -5567,10 +5603,10 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>14</v>
@@ -5579,7 +5615,7 @@
         <v>332</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>16</v>
@@ -5592,13 +5628,13 @@
         <v>338</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J48" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K48" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I48,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I48,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="L48" s="4"/>
@@ -5620,10 +5656,10 @@
     </row>
     <row r="49">
       <c r="A49" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>14</v>
@@ -5632,7 +5668,7 @@
         <v>332</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>16</v>
@@ -5645,13 +5681,13 @@
         <v>339</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J49" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K49" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I49,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I49,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="L49" s="4"/>
@@ -5673,10 +5709,10 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>14</v>
@@ -5685,7 +5721,7 @@
         <v>332</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>16</v>
@@ -5698,13 +5734,13 @@
         <v>340</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J50" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K50" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I50,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I50,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="L50" s="4"/>
@@ -5726,10 +5762,10 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>14</v>
@@ -5738,7 +5774,7 @@
         <v>332</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>16</v>
@@ -5751,14 +5787,14 @@
         <v>341</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K51" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I51,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"038")</f>
-        <v>038</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I51,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <v>037</v>
       </c>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
@@ -5779,10 +5815,10 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>14</v>
@@ -5791,7 +5827,7 @@
         <v>332</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>16</v>
@@ -5804,14 +5840,14 @@
         <v>342</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="J52" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K52" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I52,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"039")</f>
-        <v>039</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I52,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"038")</f>
+        <v>038</v>
       </c>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
@@ -5832,10 +5868,10 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>14</v>
@@ -5844,7 +5880,7 @@
         <v>332</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>16</v>
@@ -5857,13 +5893,13 @@
         <v>343</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="J53" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K53" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I53,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"039")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I53,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"039")</f>
         <v>039</v>
       </c>
       <c r="L53" s="4"/>
@@ -5885,10 +5921,10 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>14</v>
@@ -5897,27 +5933,27 @@
         <v>332</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G54" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>LOP</v>
+        <v>ROP</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>344</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="J54" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K54" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I54,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"040")</f>
-        <v>040</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I54,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"039")</f>
+        <v>039</v>
       </c>
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
@@ -5938,10 +5974,10 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>14</v>
@@ -5950,27 +5986,27 @@
         <v>332</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G55" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>ROP</v>
+        <v>LOP</v>
       </c>
       <c r="H55" s="5" t="s">
         <v>345</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="J55" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K55" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I55,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"041")</f>
-        <v>041</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I55,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"040")</f>
+        <v>040</v>
       </c>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
@@ -5991,10 +6027,10 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>14</v>
@@ -6003,7 +6039,7 @@
         <v>332</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>16</v>
@@ -6016,14 +6052,14 @@
         <v>346</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="J56" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K56" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I56,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"042")</f>
-        <v>042</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I56,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"041")</f>
+        <v>041</v>
       </c>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
@@ -6044,10 +6080,10 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>14</v>
@@ -6056,27 +6092,27 @@
         <v>332</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G57" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>LOP</v>
+        <v>ROP</v>
       </c>
       <c r="H57" s="5" t="s">
         <v>347</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="J57" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K57" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I57,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"043")</f>
-        <v>043</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I57,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"042")</f>
+        <v>042</v>
       </c>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
@@ -6097,10 +6133,10 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>14</v>
@@ -6109,10 +6145,10 @@
         <v>332</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G58" s="5" t="str">
         <f t="shared" si="1"/>
@@ -6122,13 +6158,13 @@
         <v>348</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J58" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K58" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I58,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"043")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I58,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"043")</f>
         <v>043</v>
       </c>
       <c r="L58" s="4"/>
@@ -6150,10 +6186,10 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>14</v>
@@ -6162,10 +6198,10 @@
         <v>332</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G59" s="5" t="str">
         <f t="shared" si="1"/>
@@ -6175,14 +6211,14 @@
         <v>349</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K59" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I59,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"044")</f>
-        <v>044</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I59,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"043")</f>
+        <v>043</v>
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
@@ -6203,10 +6239,10 @@
     </row>
     <row r="60">
       <c r="A60" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>14</v>
@@ -6215,27 +6251,27 @@
         <v>332</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G60" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>ROP</v>
+        <v>LOP</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>350</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="J60" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K60" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I60,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"045")</f>
-        <v>045</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I60,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"044")</f>
+        <v>044</v>
       </c>
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
@@ -6256,10 +6292,10 @@
     </row>
     <row r="61">
       <c r="A61" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>14</v>
@@ -6268,27 +6304,27 @@
         <v>332</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G61" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>LOP</v>
+        <v>ROP</v>
       </c>
       <c r="H61" s="5" t="s">
         <v>351</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="J61" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K61" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I61,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"046")</f>
-        <v>046</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I61,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"045")</f>
+        <v>045</v>
       </c>
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
@@ -6309,10 +6345,10 @@
     </row>
     <row r="62">
       <c r="A62" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>14</v>
@@ -6321,10 +6357,10 @@
         <v>332</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G62" s="5" t="str">
         <f t="shared" si="1"/>
@@ -6334,14 +6370,14 @@
         <v>352</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="J62" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K62" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I62,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"047")</f>
-        <v>047</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I62,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"046")</f>
+        <v>046</v>
       </c>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
@@ -6362,10 +6398,10 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>14</v>
@@ -6374,27 +6410,27 @@
         <v>332</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G63" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>ROP</v>
+        <v>LOP</v>
       </c>
       <c r="H63" s="5" t="s">
         <v>353</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="J63" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K63" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I63,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"048")</f>
-        <v>048</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I63,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"047")</f>
+        <v>047</v>
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
@@ -6415,39 +6451,39 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G64" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>LOP</v>
+        <v>ROP</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="J64" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K64" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I64,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"049")</f>
-        <v>049</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I64,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"048")</f>
+        <v>048</v>
       </c>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
@@ -6468,22 +6504,22 @@
     </row>
     <row r="65">
       <c r="A65" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G65" s="5" t="str">
         <f t="shared" si="1"/>
@@ -6493,14 +6529,14 @@
         <v>356</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K65" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I65,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"050")</f>
-        <v>050</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I65,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"049")</f>
+        <v>049</v>
       </c>
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
@@ -6521,22 +6557,22 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G66" s="5" t="str">
         <f t="shared" si="1"/>
@@ -6546,14 +6582,14 @@
         <v>357</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K66" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I66,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"051")</f>
-        <v>051</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I66,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"050")</f>
+        <v>050</v>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
@@ -6574,22 +6610,22 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G67" s="5" t="str">
         <f t="shared" si="1"/>
@@ -6599,14 +6635,14 @@
         <v>358</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K67" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I67,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"052")</f>
-        <v>052</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I67,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"051")</f>
+        <v>051</v>
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
@@ -6627,39 +6663,39 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>193</v>
+        <v>14</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G68" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>ROP</v>
+        <v>LOP</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K68" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I68,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"053")</f>
-        <v>053</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I68,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"052")</f>
+        <v>052</v>
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
@@ -6680,19 +6716,19 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>16</v>
@@ -6705,13 +6741,13 @@
         <v>361</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K69" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I69,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"053")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I69,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"053")</f>
         <v>053</v>
       </c>
       <c r="L69" s="4"/>
@@ -6733,19 +6769,19 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>16</v>
@@ -6758,13 +6794,13 @@
         <v>362</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K70" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I70,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"053")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I70,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"053")</f>
         <v>053</v>
       </c>
       <c r="L70" s="4"/>
@@ -6786,19 +6822,19 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>16</v>
@@ -6811,13 +6847,13 @@
         <v>363</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K71" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I71,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"053")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I71,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"053")</f>
         <v>053</v>
       </c>
       <c r="L71" s="4"/>
@@ -6839,19 +6875,19 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>16</v>
@@ -6864,13 +6900,13 @@
         <v>364</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K72" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I72,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"053")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I72,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"053")</f>
         <v>053</v>
       </c>
       <c r="L72" s="4"/>
@@ -6892,19 +6928,19 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>16</v>
@@ -6914,17 +6950,17 @@
         <v>ROP</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K73" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I73,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"054")</f>
-        <v>054</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I73,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"053")</f>
+        <v>053</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
@@ -6945,39 +6981,39 @@
     </row>
     <row r="74">
       <c r="A74" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G74" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>LOP</v>
+        <v>ROP</v>
       </c>
       <c r="H74" s="5" t="s">
         <v>367</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K74" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I74,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"055")</f>
-        <v>055</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I74,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"054")</f>
+        <v>054</v>
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
@@ -6998,39 +7034,39 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>14</v>
+        <v>192</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G75" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K75" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I75,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"056")</f>
-        <v>056</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I75,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"055")</f>
+        <v>055</v>
       </c>
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
@@ -7051,22 +7087,22 @@
     </row>
     <row r="76">
       <c r="A76" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G76" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7076,14 +7112,14 @@
         <v>370</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K76" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I76,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"057")</f>
-        <v>057</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I76,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"056")</f>
+        <v>056</v>
       </c>
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
@@ -7104,39 +7140,39 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G77" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>ROP</v>
+        <v>LOP</v>
       </c>
       <c r="H77" s="5" t="s">
         <v>371</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>372</v>
+        <v>19</v>
       </c>
       <c r="K77" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I77,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"058")</f>
-        <v>058</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I77,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"057")</f>
+        <v>057</v>
       </c>
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
@@ -7157,19 +7193,19 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>16</v>
@@ -7179,17 +7215,17 @@
         <v>ROP</v>
       </c>
       <c r="H78" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="J78" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="I78" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="J78" s="5" t="s">
-        <v>372</v>
-      </c>
       <c r="K78" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I78,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"059")</f>
-        <v>059</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I78,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"058")</f>
+        <v>058</v>
       </c>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
@@ -7210,19 +7246,19 @@
     </row>
     <row r="79">
       <c r="A79" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>16</v>
@@ -7235,14 +7271,14 @@
         <v>374</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>19</v>
+        <v>373</v>
       </c>
       <c r="K79" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I79,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"060")</f>
-        <v>060</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I79,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"059")</f>
+        <v>059</v>
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
@@ -7263,19 +7299,19 @@
     </row>
     <row r="80">
       <c r="A80" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>16</v>
@@ -7288,14 +7324,14 @@
         <v>375</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K80" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I80,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"061")</f>
-        <v>061</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I80,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"060")</f>
+        <v>060</v>
       </c>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
@@ -7316,19 +7352,19 @@
     </row>
     <row r="81">
       <c r="A81" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>16</v>
@@ -7341,14 +7377,14 @@
         <v>376</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K81" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I81,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"062")</f>
-        <v>062</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I81,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"061")</f>
+        <v>061</v>
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
@@ -7369,19 +7405,19 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>16</v>
@@ -7394,14 +7430,14 @@
         <v>377</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K82" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I82,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"063")</f>
-        <v>063</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I82,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"062")</f>
+        <v>062</v>
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
@@ -7422,39 +7458,39 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>226</v>
+        <v>14</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G83" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>LOP</v>
+        <v>ROP</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K83" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I83,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"064")</f>
-        <v>064</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I83,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"063")</f>
+        <v>063</v>
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
@@ -7475,22 +7511,22 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G84" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7500,13 +7536,13 @@
         <v>380</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="J84" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K84" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I84,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I84,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="L84" s="4"/>
@@ -7528,39 +7564,39 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="s">
-        <v>240</v>
+        <v>198</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="C85" s="9" t="s">
-        <v>14</v>
+        <v>199</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G85" s="5" t="str">
         <f t="shared" si="1"/>
         <v>LOP</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="J85" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K85" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I85,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"065")</f>
-        <v>065</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I85,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <v>064</v>
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
@@ -7581,39 +7617,39 @@
     </row>
     <row r="86">
       <c r="A86" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C86" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G86" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>ROP</v>
+        <v>LOP</v>
       </c>
       <c r="H86" s="5" t="s">
         <v>383</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="J86" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K86" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I86,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"066")</f>
-        <v>066</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I86,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"065")</f>
+        <v>065</v>
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
@@ -7634,19 +7670,19 @@
     </row>
     <row r="87">
       <c r="A87" s="5" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>16</v>
@@ -7656,17 +7692,17 @@
         <v>ROP</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="J87" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K87" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I87,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"067")</f>
-        <v>067</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I87,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"066")</f>
+        <v>066</v>
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
@@ -7687,19 +7723,19 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>16</v>
@@ -7712,13 +7748,13 @@
         <v>386</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K88" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I88,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"067")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I88,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"067")</f>
         <v>067</v>
       </c>
       <c r="L88" s="4"/>
@@ -7740,19 +7776,19 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>16</v>
@@ -7761,18 +7797,18 @@
         <f t="shared" si="1"/>
         <v>ROP</v>
       </c>
-      <c r="H89" s="12" t="s">
-        <v>388</v>
+      <c r="H89" s="5" t="s">
+        <v>387</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="J89" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K89" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I89,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"068")</f>
-        <v>068</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I89,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"067")</f>
+        <v>067</v>
       </c>
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
@@ -7793,19 +7829,19 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C90" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>16</v>
@@ -7818,14 +7854,14 @@
         <v>389</v>
       </c>
       <c r="I90" s="5" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="J90" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K90" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I90,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"069")</f>
-        <v>069</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I90,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"068")</f>
+        <v>068</v>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
@@ -7846,19 +7882,19 @@
     </row>
     <row r="91">
       <c r="A91" s="5" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C91" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>16</v>
@@ -7867,18 +7903,18 @@
         <f t="shared" si="1"/>
         <v>ROP</v>
       </c>
-      <c r="H91" s="5" t="s">
+      <c r="H91" s="12" t="s">
         <v>390</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="J91" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K91" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I91,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"070")</f>
-        <v>070</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I91,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"069")</f>
+        <v>069</v>
       </c>
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
@@ -7899,39 +7935,39 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C92" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G92" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>LOP</v>
+        <v>ROP</v>
       </c>
       <c r="H92" s="5" t="s">
         <v>391</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="J92" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K92" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I92,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"071")</f>
-        <v>071</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I92,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"070")</f>
+        <v>070</v>
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
@@ -7952,22 +7988,22 @@
     </row>
     <row r="93">
       <c r="A93" s="5" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C93" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G93" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7977,14 +8013,14 @@
         <v>392</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="J93" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K93" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I93,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"072")</f>
-        <v>072</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I93,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"071")</f>
+        <v>071</v>
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
@@ -8005,22 +8041,22 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C94" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G94" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8030,14 +8066,14 @@
         <v>393</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="J94" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K94" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I94,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"073")</f>
-        <v>073</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I94,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"072")</f>
+        <v>072</v>
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
@@ -8058,39 +8094,39 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G95" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>ROP</v>
+        <v>LOP</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I95" s="5" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>396</v>
+        <v>19</v>
       </c>
       <c r="K95" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I95,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"074")</f>
-        <v>074</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I95,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"073")</f>
+        <v>073</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
@@ -8111,19 +8147,19 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="s">
-        <v>271</v>
+        <v>246</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>172</v>
+        <v>247</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>262</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="F96" s="5" t="s">
         <v>16</v>
@@ -8133,17 +8169,17 @@
         <v>ROP</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="I96" s="5" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="K96" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I96,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"075")</f>
-        <v>075</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I96,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"074")</f>
+        <v>074</v>
       </c>
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
@@ -8164,19 +8200,19 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>16</v>
@@ -8189,13 +8225,13 @@
         <v>399</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J97" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K97" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I97,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"075")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I97,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"075")</f>
         <v>075</v>
       </c>
       <c r="L97" s="4"/>
@@ -8217,19 +8253,19 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>16</v>
@@ -8242,13 +8278,13 @@
         <v>400</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J98" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K98" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I98,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"075")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I98,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"075")</f>
         <v>075</v>
       </c>
       <c r="L98" s="4"/>
@@ -8270,19 +8306,19 @@
     </row>
     <row r="99">
       <c r="A99" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F99" s="5" t="s">
         <v>16</v>
@@ -8295,13 +8331,13 @@
         <v>401</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K99" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I99,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"075")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I99,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"075")</f>
         <v>075</v>
       </c>
       <c r="L99" s="4"/>
@@ -8323,19 +8359,19 @@
     </row>
     <row r="100">
       <c r="A100" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F100" s="5" t="s">
         <v>16</v>
@@ -8348,14 +8384,14 @@
         <v>402</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K100" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I100,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"076")</f>
-        <v>076</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I100,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"075")</f>
+        <v>075</v>
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
@@ -8376,19 +8412,19 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>16</v>
@@ -8401,13 +8437,13 @@
         <v>403</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K101" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I101,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"076")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I101,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"076")</f>
         <v>076</v>
       </c>
       <c r="L101" s="4"/>
@@ -8429,19 +8465,19 @@
     </row>
     <row r="102">
       <c r="A102" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>16</v>
@@ -8454,14 +8490,14 @@
         <v>404</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K102" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I102,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"077")</f>
-        <v>077</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I102,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"076")</f>
+        <v>076</v>
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="4"/>
@@ -8482,39 +8518,39 @@
     </row>
     <row r="103">
       <c r="A103" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G103" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>LOP</v>
+        <v>ROP</v>
       </c>
       <c r="H103" s="5" t="s">
         <v>405</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>19</v>
+        <v>373</v>
       </c>
       <c r="K103" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I103,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"078")</f>
-        <v>078</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I103,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"077")</f>
+        <v>077</v>
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
@@ -8535,22 +8571,22 @@
     </row>
     <row r="104">
       <c r="A104" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G104" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8560,14 +8596,14 @@
         <v>406</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K104" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I104,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"079")</f>
-        <v>079</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I104,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"078")</f>
+        <v>078</v>
       </c>
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
@@ -8588,22 +8624,22 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G105" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8613,14 +8649,14 @@
         <v>407</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="J105" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K105" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I105,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"080")</f>
-        <v>080</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I105,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"079")</f>
+        <v>079</v>
       </c>
       <c r="L105" s="4"/>
       <c r="M105" s="4"/>
@@ -8641,39 +8677,39 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G106" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>ROP</v>
+        <v>LOP</v>
       </c>
       <c r="H106" s="5" t="s">
         <v>408</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="J106" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K106" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I106,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"081")</f>
-        <v>081</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I106,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"080")</f>
+        <v>080</v>
       </c>
       <c r="L106" s="4"/>
       <c r="M106" s="4"/>
@@ -8694,19 +8730,19 @@
     </row>
     <row r="107">
       <c r="A107" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>16</v>
@@ -8719,14 +8755,14 @@
         <v>409</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="J107" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K107" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I107,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"082")</f>
-        <v>082</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I107,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"081")</f>
+        <v>081</v>
       </c>
       <c r="L107" s="4"/>
       <c r="M107" s="4"/>
@@ -8747,39 +8783,39 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G108" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>LOP</v>
+        <v>ROP</v>
       </c>
       <c r="H108" s="5" t="s">
         <v>410</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J108" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K108" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I108,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"083")</f>
-        <v>083</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I108,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"082")</f>
+        <v>082</v>
       </c>
       <c r="L108" s="4"/>
       <c r="M108" s="4"/>
@@ -8798,24 +8834,24 @@
       <c r="Z108" s="4"/>
       <c r="AA108" s="4"/>
     </row>
-    <row r="109" ht="60.0" customHeight="1">
+    <row r="109">
       <c r="A109" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G109" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8825,14 +8861,14 @@
         <v>411</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="J109" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K109" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I109,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"084")</f>
-        <v>084</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I109,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"083")</f>
+        <v>083</v>
       </c>
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
@@ -8851,41 +8887,41 @@
       <c r="Z109" s="4"/>
       <c r="AA109" s="4"/>
     </row>
-    <row r="110">
+    <row r="110" ht="60.0" customHeight="1">
       <c r="A110" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G110" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>ROP</v>
+        <v>LOP</v>
       </c>
       <c r="H110" s="5" t="s">
         <v>412</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="J110" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K110" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I110,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"085")</f>
-        <v>085</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I110,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"084")</f>
+        <v>084</v>
       </c>
       <c r="L110" s="4"/>
       <c r="M110" s="4"/>
@@ -8906,39 +8942,39 @@
     </row>
     <row r="111">
       <c r="A111" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G111" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>LOP</v>
+        <v>ROP</v>
       </c>
       <c r="H111" s="5" t="s">
         <v>413</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="J111" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K111" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I111,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"086")</f>
-        <v>086</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I111,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"085")</f>
+        <v>085</v>
       </c>
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
@@ -8959,22 +8995,22 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G112" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8984,14 +9020,14 @@
         <v>414</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="J112" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K112" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I112,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"087")</f>
-        <v>087</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I112,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"086")</f>
+        <v>086</v>
       </c>
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
@@ -9012,39 +9048,39 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G113" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>ROP</v>
+        <v>LOP</v>
       </c>
       <c r="H113" s="5" t="s">
         <v>415</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="J113" s="5" t="s">
-        <v>372</v>
+        <v>19</v>
       </c>
       <c r="K113" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I113,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"088")</f>
-        <v>088</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I113,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"087")</f>
+        <v>087</v>
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="4"/>
@@ -9065,19 +9101,19 @@
     </row>
     <row r="114">
       <c r="A114" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>16</v>
@@ -9090,14 +9126,14 @@
         <v>416</v>
       </c>
       <c r="I114" s="5" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="J114" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K114" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I114,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"089")</f>
-        <v>089</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I114,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"088")</f>
+        <v>088</v>
       </c>
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
@@ -9118,19 +9154,19 @@
     </row>
     <row r="115">
       <c r="A115" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F115" s="5" t="s">
         <v>16</v>
@@ -9143,14 +9179,14 @@
         <v>417</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="J115" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K115" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I115,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"090")</f>
-        <v>090</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I115,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"089")</f>
+        <v>089</v>
       </c>
       <c r="L115" s="4"/>
       <c r="M115" s="4"/>
@@ -9171,39 +9207,39 @@
     </row>
     <row r="116">
       <c r="A116" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G116" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>LOP</v>
+        <v>ROP</v>
       </c>
       <c r="H116" s="5" t="s">
         <v>418</v>
       </c>
       <c r="I116" s="5" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="J116" s="5" t="s">
-        <v>19</v>
+        <v>373</v>
       </c>
       <c r="K116" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I116,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"091")</f>
-        <v>091</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I116,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"090")</f>
+        <v>090</v>
       </c>
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
@@ -9224,22 +9260,22 @@
     </row>
     <row r="117">
       <c r="A117" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G117" s="5" t="str">
         <f t="shared" si="1"/>
@@ -9249,14 +9285,14 @@
         <v>419</v>
       </c>
       <c r="I117" s="5" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="J117" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K117" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I117,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"092")</f>
-        <v>092</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I117,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"091")</f>
+        <v>091</v>
       </c>
       <c r="L117" s="4"/>
       <c r="M117" s="4"/>
@@ -9277,39 +9313,39 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="s">
-        <v>317</v>
+        <v>266</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>318</v>
+        <v>267</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>14</v>
+        <v>166</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>318</v>
+        <v>268</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G118" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>ROP</v>
+        <v>LOP</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I118" s="5" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="J118" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K118" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I118,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"093")</f>
-        <v>093</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I118,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"092")</f>
+        <v>092</v>
       </c>
       <c r="L118" s="4"/>
       <c r="M118" s="4"/>
@@ -9330,19 +9366,19 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>16</v>
@@ -9355,14 +9391,14 @@
         <v>422</v>
       </c>
       <c r="I119" s="5" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="J119" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K119" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I119,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"094")</f>
-        <v>094</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I119,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"093")</f>
+        <v>093</v>
       </c>
       <c r="L119" s="4"/>
       <c r="M119" s="4"/>
@@ -9383,19 +9419,19 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="F120" s="5" t="s">
         <v>16</v>
@@ -9408,14 +9444,14 @@
         <v>423</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="J120" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K120" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I120,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"095")</f>
-        <v>095</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I120,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"094")</f>
+        <v>094</v>
       </c>
       <c r="L120" s="4"/>
       <c r="M120" s="4"/>
@@ -9436,39 +9472,39 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G121" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>LOP</v>
+        <v>ROP</v>
       </c>
       <c r="H121" s="5" t="s">
         <v>424</v>
       </c>
       <c r="I121" s="5" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="J121" s="5" t="s">
         <v>19</v>
       </c>
       <c r="K121" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I121,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"096")</f>
-        <v>096</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I121,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"095")</f>
+        <v>095</v>
       </c>
       <c r="L121" s="4"/>
       <c r="M121" s="4"/>
@@ -9489,39 +9525,39 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="s">
-        <v>62</v>
+        <v>309</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>63</v>
+        <v>310</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D122" s="5" t="s">
-        <v>425</v>
+      <c r="D122" s="6" t="s">
+        <v>421</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>63</v>
+        <v>310</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G122" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>ROP</v>
+        <v>LOP</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I122" s="5" t="s">
-        <v>65</v>
+        <v>318</v>
       </c>
       <c r="J122" s="5" t="s">
-        <v>396</v>
+        <v>19</v>
       </c>
       <c r="K122" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I122,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"097")</f>
-        <v>097</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I122,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"096")</f>
+        <v>096</v>
       </c>
       <c r="L122" s="4"/>
       <c r="M122" s="4"/>
@@ -9542,19 +9578,19 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>16</v>
@@ -9567,14 +9603,14 @@
         <v>427</v>
       </c>
       <c r="I123" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J123" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K123" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I123,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"098")</f>
-        <v>098</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I123,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"097")</f>
+        <v>097</v>
       </c>
       <c r="L123" s="4"/>
       <c r="M123" s="4"/>
@@ -9595,19 +9631,19 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B124" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>16</v>
@@ -9620,14 +9656,14 @@
         <v>428</v>
       </c>
       <c r="I124" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J124" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K124" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I124,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"099")</f>
-        <v>099</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I124,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"098")</f>
+        <v>098</v>
       </c>
       <c r="L124" s="4"/>
       <c r="M124" s="4"/>
@@ -9648,19 +9684,19 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B125" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>16</v>
@@ -9673,14 +9709,14 @@
         <v>429</v>
       </c>
       <c r="I125" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J125" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K125" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I125,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"100")</f>
-        <v>100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I125,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"099")</f>
+        <v>099</v>
       </c>
       <c r="L125" s="4"/>
       <c r="M125" s="4"/>
@@ -9701,19 +9737,19 @@
     </row>
     <row r="126">
       <c r="A126" s="5" t="s">
-        <v>230</v>
+        <v>61</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>231</v>
+        <v>62</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>232</v>
+        <v>62</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>16</v>
@@ -9723,17 +9759,17 @@
         <v>ROP</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I126" s="5" t="s">
-        <v>234</v>
+        <v>71</v>
       </c>
       <c r="J126" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K126" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I126,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"101")</f>
-        <v>101</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I126,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"100")</f>
+        <v>100</v>
       </c>
       <c r="L126" s="4"/>
       <c r="M126" s="4"/>
@@ -9754,19 +9790,19 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="s">
-        <v>230</v>
+        <v>61</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>231</v>
+        <v>62</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>232</v>
+        <v>62</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>16</v>
@@ -9776,17 +9812,17 @@
         <v>ROP</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>234</v>
+        <v>71</v>
       </c>
       <c r="J127" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K127" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I127,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"101")</f>
-        <v>101</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I127,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"100")</f>
+        <v>100</v>
       </c>
       <c r="L127" s="4"/>
       <c r="M127" s="4"/>
@@ -9807,19 +9843,19 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>16</v>
@@ -9832,14 +9868,14 @@
         <v>433</v>
       </c>
       <c r="I128" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="J128" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K128" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I128,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"102")</f>
-        <v>102</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I128,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"101")</f>
+        <v>101</v>
       </c>
       <c r="L128" s="4"/>
       <c r="M128" s="4"/>
@@ -9860,19 +9896,19 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>16</v>
@@ -9885,14 +9921,14 @@
         <v>434</v>
       </c>
       <c r="I129" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="J129" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K129" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I129,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"102")</f>
-        <v>102</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I129,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"101")</f>
+        <v>101</v>
       </c>
       <c r="L129" s="4"/>
       <c r="M129" s="4"/>
@@ -9913,19 +9949,19 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>16</v>
@@ -9938,13 +9974,13 @@
         <v>435</v>
       </c>
       <c r="I130" s="5" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J130" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K130" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I130,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"102")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I130,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"102")</f>
         <v>102</v>
       </c>
       <c r="L130" s="4"/>
@@ -9966,19 +10002,19 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>16</v>
@@ -9991,14 +10027,14 @@
         <v>436</v>
       </c>
       <c r="I131" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="J131" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K131" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I131,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"103")</f>
-        <v>103</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I131,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"102")</f>
+        <v>102</v>
       </c>
       <c r="L131" s="4"/>
       <c r="M131" s="4"/>
@@ -10019,19 +10055,19 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>16</v>
@@ -10044,14 +10080,14 @@
         <v>437</v>
       </c>
       <c r="I132" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="J132" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K132" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I132,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"103")</f>
-        <v>103</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I132,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"102")</f>
+        <v>102</v>
       </c>
       <c r="L132" s="4"/>
       <c r="M132" s="4"/>
@@ -10072,19 +10108,19 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>16</v>
@@ -10097,13 +10133,13 @@
         <v>438</v>
       </c>
       <c r="I133" s="5" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="J133" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K133" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I133,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"103")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I133,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"103")</f>
         <v>103</v>
       </c>
       <c r="L133" s="4"/>
@@ -10125,19 +10161,19 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="s">
-        <v>96</v>
+        <v>226</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>97</v>
+        <v>227</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>125</v>
+        <v>14</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>290</v>
+        <v>432</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>126</v>
+        <v>228</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>16</v>
@@ -10150,14 +10186,14 @@
         <v>439</v>
       </c>
       <c r="I134" s="5" t="s">
-        <v>440</v>
+        <v>234</v>
       </c>
       <c r="J134" s="5" t="s">
-        <v>441</v>
+        <v>397</v>
       </c>
       <c r="K134" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I134,UNIQUE(FILTER($I$2:$I1062,$I$2:$I1062&lt;&gt;"""")),0),""000"")"),"104")</f>
-        <v>104</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I134,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"103")</f>
+        <v>103</v>
       </c>
       <c r="L134" s="4"/>
       <c r="M134" s="4"/>
@@ -10177,17 +10213,41 @@
       <c r="AA134" s="4"/>
     </row>
     <row r="135">
-      <c r="A135" s="6"/>
-      <c r="B135" s="6"/>
-      <c r="C135" s="6"/>
-      <c r="D135" s="6"/>
-      <c r="E135" s="6"/>
-      <c r="F135" s="6"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="6"/>
-      <c r="I135" s="6"/>
-      <c r="J135" s="4"/>
-      <c r="K135" s="4"/>
+      <c r="A135" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G135" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>ROP</v>
+      </c>
+      <c r="H135" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="I135" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="J135" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="K135" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I135,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"103")</f>
+        <v>103</v>
+      </c>
       <c r="L135" s="4"/>
       <c r="M135" s="4"/>
       <c r="N135" s="4"/>
@@ -10206,17 +10266,41 @@
       <c r="AA135" s="4"/>
     </row>
     <row r="136">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6"/>
-      <c r="C136" s="6"/>
-      <c r="D136" s="6"/>
-      <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
-      <c r="G136" s="6"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6"/>
-      <c r="J136" s="4"/>
-      <c r="K136" s="4"/>
+      <c r="A136" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G136" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>ROP</v>
+      </c>
+      <c r="H136" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="I136" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="J136" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="K136" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(I136,UNIQUE(FILTER($I$2:$I1064,$I$2:$I1064&lt;&gt;"""")),0),""000"")"),"104")</f>
+        <v>104</v>
+      </c>
       <c r="L136" s="4"/>
       <c r="M136" s="4"/>
       <c r="N136" s="4"/>
@@ -10243,6 +10327,7 @@
       <c r="F137" s="6"/>
       <c r="G137" s="6"/>
       <c r="H137" s="6"/>
+      <c r="I137" s="6"/>
       <c r="J137" s="4"/>
       <c r="K137" s="4"/>
       <c r="L137" s="4"/>
@@ -10300,7 +10385,6 @@
       <c r="F139" s="6"/>
       <c r="G139" s="6"/>
       <c r="H139" s="6"/>
-      <c r="I139" s="6"/>
       <c r="J139" s="4"/>
       <c r="K139" s="4"/>
       <c r="L139" s="4"/>
@@ -11046,15 +11130,15 @@
       <c r="AA164" s="4"/>
     </row>
     <row r="165">
-      <c r="A165" s="13"/>
-      <c r="B165" s="13"/>
-      <c r="C165" s="13"/>
-      <c r="D165" s="13"/>
-      <c r="E165" s="13"/>
-      <c r="F165" s="13"/>
-      <c r="G165" s="13"/>
-      <c r="H165" s="13"/>
-      <c r="I165" s="13"/>
+      <c r="A165" s="6"/>
+      <c r="B165" s="6"/>
+      <c r="C165" s="6"/>
+      <c r="D165" s="6"/>
+      <c r="E165" s="6"/>
+      <c r="F165" s="6"/>
+      <c r="G165" s="6"/>
+      <c r="H165" s="6"/>
+      <c r="I165" s="6"/>
       <c r="J165" s="4"/>
       <c r="K165" s="4"/>
       <c r="L165" s="4"/>
@@ -11075,15 +11159,15 @@
       <c r="AA165" s="4"/>
     </row>
     <row r="166">
-      <c r="A166" s="13"/>
-      <c r="B166" s="13"/>
-      <c r="C166" s="13"/>
-      <c r="D166" s="13"/>
-      <c r="E166" s="13"/>
-      <c r="F166" s="13"/>
-      <c r="G166" s="13"/>
-      <c r="H166" s="13"/>
-      <c r="I166" s="13"/>
+      <c r="A166" s="6"/>
+      <c r="B166" s="6"/>
+      <c r="C166" s="6"/>
+      <c r="D166" s="6"/>
+      <c r="E166" s="6"/>
+      <c r="F166" s="6"/>
+      <c r="G166" s="6"/>
+      <c r="H166" s="6"/>
+      <c r="I166" s="6"/>
       <c r="J166" s="4"/>
       <c r="K166" s="4"/>
       <c r="L166" s="4"/>
@@ -11394,15 +11478,15 @@
       <c r="AA176" s="4"/>
     </row>
     <row r="177">
-      <c r="A177" s="4"/>
-      <c r="B177" s="4"/>
-      <c r="C177" s="4"/>
-      <c r="D177" s="4"/>
-      <c r="E177" s="4"/>
-      <c r="F177" s="4"/>
-      <c r="G177" s="4"/>
-      <c r="H177" s="4"/>
-      <c r="I177" s="4"/>
+      <c r="A177" s="13"/>
+      <c r="B177" s="13"/>
+      <c r="C177" s="13"/>
+      <c r="D177" s="13"/>
+      <c r="E177" s="13"/>
+      <c r="F177" s="13"/>
+      <c r="G177" s="13"/>
+      <c r="H177" s="13"/>
+      <c r="I177" s="13"/>
       <c r="J177" s="4"/>
       <c r="K177" s="4"/>
       <c r="L177" s="4"/>
@@ -11423,15 +11507,15 @@
       <c r="AA177" s="4"/>
     </row>
     <row r="178">
-      <c r="A178" s="4"/>
-      <c r="B178" s="4"/>
-      <c r="C178" s="4"/>
-      <c r="D178" s="4"/>
-      <c r="E178" s="4"/>
-      <c r="F178" s="4"/>
-      <c r="G178" s="4"/>
-      <c r="H178" s="4"/>
-      <c r="I178" s="4"/>
+      <c r="A178" s="13"/>
+      <c r="B178" s="13"/>
+      <c r="C178" s="13"/>
+      <c r="D178" s="13"/>
+      <c r="E178" s="13"/>
+      <c r="F178" s="13"/>
+      <c r="G178" s="13"/>
+      <c r="H178" s="13"/>
+      <c r="I178" s="13"/>
       <c r="J178" s="4"/>
       <c r="K178" s="4"/>
       <c r="L178" s="4"/>
@@ -37087,8 +37171,66 @@
       <c r="Z1062" s="4"/>
       <c r="AA1062" s="4"/>
     </row>
+    <row r="1063">
+      <c r="A1063" s="4"/>
+      <c r="B1063" s="4"/>
+      <c r="C1063" s="4"/>
+      <c r="D1063" s="4"/>
+      <c r="E1063" s="4"/>
+      <c r="F1063" s="4"/>
+      <c r="G1063" s="4"/>
+      <c r="H1063" s="4"/>
+      <c r="I1063" s="4"/>
+      <c r="J1063" s="4"/>
+      <c r="K1063" s="4"/>
+      <c r="L1063" s="4"/>
+      <c r="M1063" s="4"/>
+      <c r="N1063" s="4"/>
+      <c r="O1063" s="4"/>
+      <c r="P1063" s="4"/>
+      <c r="Q1063" s="4"/>
+      <c r="R1063" s="4"/>
+      <c r="S1063" s="4"/>
+      <c r="T1063" s="4"/>
+      <c r="U1063" s="4"/>
+      <c r="V1063" s="4"/>
+      <c r="W1063" s="4"/>
+      <c r="X1063" s="4"/>
+      <c r="Y1063" s="4"/>
+      <c r="Z1063" s="4"/>
+      <c r="AA1063" s="4"/>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="4"/>
+      <c r="B1064" s="4"/>
+      <c r="C1064" s="4"/>
+      <c r="D1064" s="4"/>
+      <c r="E1064" s="4"/>
+      <c r="F1064" s="4"/>
+      <c r="G1064" s="4"/>
+      <c r="H1064" s="4"/>
+      <c r="I1064" s="4"/>
+      <c r="J1064" s="4"/>
+      <c r="K1064" s="4"/>
+      <c r="L1064" s="4"/>
+      <c r="M1064" s="4"/>
+      <c r="N1064" s="4"/>
+      <c r="O1064" s="4"/>
+      <c r="P1064" s="4"/>
+      <c r="Q1064" s="4"/>
+      <c r="R1064" s="4"/>
+      <c r="S1064" s="4"/>
+      <c r="T1064" s="4"/>
+      <c r="U1064" s="4"/>
+      <c r="V1064" s="4"/>
+      <c r="W1064" s="4"/>
+      <c r="X1064" s="4"/>
+      <c r="Y1064" s="4"/>
+      <c r="Z1064" s="4"/>
+      <c r="AA1064" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$K$134"/>
+  <autoFilter ref="$A$1:$K$136"/>
   <drawing r:id="rId4"/>
   <legacyDrawing r:id="rId5"/>
 </worksheet>
